--- a/cache_registry/fixtures/multi_year_licenses/combined_nomenclature.xlsx
+++ b/cache_registry/fixtures/multi_year_licenses/combined_nomenclature.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="247">
   <si>
     <t xml:space="preserve">CN code</t>
   </si>
@@ -29,6 +29,9 @@
   </si>
   <si>
     <t xml:space="preserve">substance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">corrected_name</t>
   </si>
   <si>
     <t xml:space="preserve">name</t>
@@ -276,6 +279,9 @@
     <t xml:space="preserve">Halon-1211</t>
   </si>
   <si>
+    <t xml:space="preserve">Halon 1211</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bromochlorodifluoromethane</t>
   </si>
   <si>
@@ -283,6 +289,9 @@
   </si>
   <si>
     <t xml:space="preserve">Halon-1301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Halon 1301</t>
   </si>
   <si>
     <t xml:space="preserve">Bromotrifluoromethane</t>
@@ -294,6 +303,9 @@
     <t xml:space="preserve">Halon-2402</t>
   </si>
   <si>
+    <t xml:space="preserve">Halon 2402</t>
+  </si>
+  <si>
     <t xml:space="preserve">1,2-Dibromo-1,1,2,2-tetrafluoroethane</t>
   </si>
   <si>
@@ -303,10 +315,16 @@
     <t xml:space="preserve">Halon- 1202</t>
   </si>
   <si>
+    <t xml:space="preserve">Halon 1202</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dibromodifluoromethane</t>
   </si>
   <si>
     <t xml:space="preserve">Carbon tetrachloride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTC</t>
   </si>
   <si>
     <t xml:space="preserve">Tetrachloromethane</t>
@@ -318,10 +336,16 @@
     <t xml:space="preserve">1,1,1-trichloroethane</t>
   </si>
   <si>
+    <t xml:space="preserve">TCA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bromomethane (methyl bromide)</t>
   </si>
   <si>
     <t xml:space="preserve">Methyl bromide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MB</t>
   </si>
   <si>
     <t xml:space="preserve">Bromomethane</t>
@@ -822,6 +846,9 @@
     <t xml:space="preserve">Bromochloromethane</t>
   </si>
   <si>
+    <t xml:space="preserve">BCM</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bromochloromethane (Halon 1011)</t>
   </si>
   <si>
@@ -1181,14 +1208,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:JA311"/>
+  <dimension ref="A1:JB311"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.93"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="75.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="39.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="5.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="26.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="39.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="5.92"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1204,8 +1231,10 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="3"/>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
@@ -1214,10 +1243,10 @@
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
       <c r="N1" s="3"/>
-      <c r="O1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="P1" s="4"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="Q1" s="4"/>
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
@@ -1463,22 +1492,25 @@
       <c r="IY1" s="4"/>
       <c r="IZ1" s="4"/>
       <c r="JA1" s="4"/>
+      <c r="JB1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="n">
         <v>2903776000</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="3"/>
+      <c r="E2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="6"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
@@ -1487,10 +1519,10 @@
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
-      <c r="O2" s="6" t="n">
+      <c r="O2" s="3"/>
+      <c r="P2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
@@ -1736,22 +1768,25 @@
       <c r="IY2" s="4"/>
       <c r="IZ2" s="4"/>
       <c r="JA2" s="4"/>
+      <c r="JB2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="n">
         <v>2903776000</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="3"/>
+      <c r="E3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="6"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
@@ -1760,10 +1795,10 @@
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
-      <c r="O3" s="6" t="n">
+      <c r="O3" s="3"/>
+      <c r="P3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
@@ -2009,22 +2044,25 @@
       <c r="IY3" s="4"/>
       <c r="IZ3" s="4"/>
       <c r="JA3" s="4"/>
+      <c r="JB3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="n">
         <v>2903776000</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="3"/>
+      <c r="E4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="6"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -2033,10 +2071,10 @@
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
-      <c r="O4" s="6" t="n">
+      <c r="O4" s="3"/>
+      <c r="P4" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
@@ -2282,22 +2320,25 @@
       <c r="IY4" s="4"/>
       <c r="IZ4" s="4"/>
       <c r="JA4" s="4"/>
+      <c r="JB4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="n">
         <v>2903776000</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="3"/>
+      <c r="E5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="6"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
@@ -2306,10 +2347,10 @@
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="6" t="n">
+      <c r="O5" s="3"/>
+      <c r="P5" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
@@ -2555,22 +2596,25 @@
       <c r="IY5" s="4"/>
       <c r="IZ5" s="4"/>
       <c r="JA5" s="4"/>
+      <c r="JB5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="n">
         <v>2903776000</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="3"/>
+      <c r="E6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="6"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -2579,10 +2623,10 @@
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
-      <c r="O6" s="6" t="n">
+      <c r="O6" s="3"/>
+      <c r="P6" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
@@ -2828,22 +2872,25 @@
       <c r="IY6" s="4"/>
       <c r="IZ6" s="4"/>
       <c r="JA6" s="4"/>
+      <c r="JB6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="n">
         <v>2903776000</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="3"/>
+      <c r="E7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="6"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
@@ -2852,10 +2899,10 @@
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
-      <c r="O7" s="6" t="n">
+      <c r="O7" s="3"/>
+      <c r="P7" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
@@ -3101,22 +3148,25 @@
       <c r="IY7" s="4"/>
       <c r="IZ7" s="4"/>
       <c r="JA7" s="4"/>
+      <c r="JB7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="n">
         <v>2903776000</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="3"/>
+      <c r="E8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="6"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -3125,10 +3175,10 @@
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
-      <c r="O8" s="6" t="n">
+      <c r="O8" s="3"/>
+      <c r="P8" s="6" t="n">
         <v>0.6</v>
       </c>
-      <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
@@ -3374,22 +3424,25 @@
       <c r="IY8" s="4"/>
       <c r="IZ8" s="4"/>
       <c r="JA8" s="4"/>
+      <c r="JB8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="n">
         <v>2903779060</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="3"/>
+      <c r="E9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="6"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
@@ -3398,10 +3451,10 @@
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
-      <c r="O9" s="6" t="n">
+      <c r="O9" s="3"/>
+      <c r="P9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
@@ -3647,22 +3700,25 @@
       <c r="IY9" s="4"/>
       <c r="IZ9" s="4"/>
       <c r="JA9" s="4"/>
+      <c r="JB9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="n">
         <v>2903779015</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="3"/>
+      <c r="E10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="6"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
@@ -3671,10 +3727,10 @@
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
-      <c r="O10" s="6" t="n">
+      <c r="O10" s="3"/>
+      <c r="P10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
@@ -3920,22 +3976,25 @@
       <c r="IY10" s="4"/>
       <c r="IZ10" s="4"/>
       <c r="JA10" s="4"/>
+      <c r="JB10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="n">
         <v>2903779020</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="3"/>
+      <c r="E11" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="6"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
@@ -3944,10 +4003,10 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-      <c r="O11" s="6" t="n">
+      <c r="O11" s="3"/>
+      <c r="P11" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
@@ -4193,22 +4252,25 @@
       <c r="IY11" s="4"/>
       <c r="IZ11" s="4"/>
       <c r="JA11" s="4"/>
+      <c r="JB11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="n">
         <v>2903779025</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="3"/>
+      <c r="E12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="6"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -4217,10 +4279,10 @@
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
-      <c r="O12" s="6" t="n">
+      <c r="O12" s="3"/>
+      <c r="P12" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
@@ -4466,22 +4528,25 @@
       <c r="IY12" s="4"/>
       <c r="IZ12" s="4"/>
       <c r="JA12" s="4"/>
+      <c r="JB12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="n">
         <v>2903779030</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="3"/>
+      <c r="E13" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="6"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -4490,10 +4555,10 @@
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
-      <c r="O13" s="6" t="n">
+      <c r="O13" s="3"/>
+      <c r="P13" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
@@ -4739,22 +4804,25 @@
       <c r="IY13" s="4"/>
       <c r="IZ13" s="4"/>
       <c r="JA13" s="4"/>
+      <c r="JB13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="n">
         <v>2903779035</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="3"/>
+      <c r="E14" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="6"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -4763,10 +4831,10 @@
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
-      <c r="O14" s="6" t="n">
+      <c r="O14" s="3"/>
+      <c r="P14" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
@@ -5012,22 +5080,25 @@
       <c r="IY14" s="4"/>
       <c r="IZ14" s="4"/>
       <c r="JA14" s="4"/>
+      <c r="JB14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="n">
         <v>2903779040</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="3"/>
+      <c r="E15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="6"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -5036,10 +5107,10 @@
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
-      <c r="O15" s="6" t="n">
+      <c r="O15" s="3"/>
+      <c r="P15" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
@@ -5285,22 +5356,25 @@
       <c r="IY15" s="4"/>
       <c r="IZ15" s="4"/>
       <c r="JA15" s="4"/>
+      <c r="JB15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="n">
         <v>2903779045</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="3"/>
+      <c r="E16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="6"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
@@ -5309,10 +5383,10 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-      <c r="O16" s="6" t="n">
+      <c r="O16" s="3"/>
+      <c r="P16" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
@@ -5558,22 +5632,25 @@
       <c r="IY16" s="4"/>
       <c r="IZ16" s="4"/>
       <c r="JA16" s="4"/>
+      <c r="JB16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="n">
         <v>2903779050</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="3"/>
+      <c r="E17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="6"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
@@ -5582,10 +5659,10 @@
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
-      <c r="O17" s="6" t="n">
+      <c r="O17" s="3"/>
+      <c r="P17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
@@ -5831,22 +5908,25 @@
       <c r="IY17" s="4"/>
       <c r="IZ17" s="4"/>
       <c r="JA17" s="4"/>
+      <c r="JB17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="n">
         <v>2903779055</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="3"/>
+      <c r="E18" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="6"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
@@ -5855,10 +5935,10 @@
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
-      <c r="O18" s="6" t="n">
+      <c r="O18" s="3"/>
+      <c r="P18" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
@@ -6104,22 +6184,25 @@
       <c r="IY18" s="4"/>
       <c r="IZ18" s="4"/>
       <c r="JA18" s="4"/>
+      <c r="JB18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="n">
         <v>2903761000</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="3"/>
+        <v>54</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="6"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
@@ -6128,10 +6211,10 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-      <c r="O19" s="6" t="n">
+      <c r="O19" s="3"/>
+      <c r="P19" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
@@ -6377,22 +6460,25 @@
       <c r="IY19" s="4"/>
       <c r="IZ19" s="4"/>
       <c r="JA19" s="4"/>
+      <c r="JB19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="n">
         <v>2903762000</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" s="6"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
@@ -6401,10 +6487,10 @@
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
-      <c r="O20" s="6" t="n">
+      <c r="O20" s="3"/>
+      <c r="P20" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
@@ -6650,22 +6736,25 @@
       <c r="IY20" s="4"/>
       <c r="IZ20" s="4"/>
       <c r="JA20" s="4"/>
+      <c r="JB20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="n">
         <v>2903769000</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="3"/>
+        <v>62</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F21" s="6"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
@@ -6674,10 +6763,10 @@
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
-      <c r="O21" s="6" t="n">
+      <c r="O21" s="3"/>
+      <c r="P21" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
@@ -6923,22 +7012,25 @@
       <c r="IY21" s="4"/>
       <c r="IZ21" s="4"/>
       <c r="JA21" s="4"/>
+      <c r="JB21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="n">
         <v>2903780000</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="3"/>
+        <v>66</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" s="6"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
@@ -6947,10 +7039,10 @@
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
-      <c r="O22" s="6" t="n">
+      <c r="O22" s="3"/>
+      <c r="P22" s="6" t="n">
         <v>1.25</v>
       </c>
-      <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
       <c r="R22" s="4"/>
       <c r="S22" s="4"/>
@@ -7051,7 +7143,7 @@
       <c r="DJ22" s="4"/>
       <c r="DK22" s="4"/>
       <c r="DL22" s="4"/>
-      <c r="DM22" s="7"/>
+      <c r="DM22" s="4"/>
       <c r="DN22" s="7"/>
       <c r="DO22" s="7"/>
       <c r="DP22" s="7"/>
@@ -7196,22 +7288,25 @@
       <c r="IY22" s="7"/>
       <c r="IZ22" s="7"/>
       <c r="JA22" s="7"/>
+      <c r="JB22" s="7"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="n">
         <v>2903140000</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E23" s="6"/>
-      <c r="F23" s="3"/>
+        <v>69</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="6"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
@@ -7220,10 +7315,10 @@
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
-      <c r="O23" s="6" t="n">
+      <c r="O23" s="3"/>
+      <c r="P23" s="6" t="n">
         <v>1.1</v>
       </c>
-      <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
       <c r="R23" s="4"/>
       <c r="S23" s="4"/>
@@ -7469,22 +7564,25 @@
       <c r="IY23" s="4"/>
       <c r="IZ23" s="4"/>
       <c r="JA23" s="4"/>
+      <c r="JB23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="n">
         <v>2903190010</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="E24" s="6"/>
-      <c r="F24" s="3"/>
+        <v>73</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F24" s="6"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
@@ -7493,10 +7591,10 @@
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
-      <c r="O24" s="6" t="n">
+      <c r="O24" s="3"/>
+      <c r="P24" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
       <c r="R24" s="4"/>
       <c r="S24" s="4"/>
@@ -7742,22 +7840,25 @@
       <c r="IY24" s="4"/>
       <c r="IZ24" s="4"/>
       <c r="JA24" s="4"/>
+      <c r="JB24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="n">
         <v>2903610000</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E25" s="6"/>
-      <c r="F25" s="3"/>
+        <v>76</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F25" s="6"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
@@ -7766,10 +7867,10 @@
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
-      <c r="O25" s="6" t="n">
+      <c r="O25" s="3"/>
+      <c r="P25" s="6" t="n">
         <v>0.6</v>
       </c>
-      <c r="P25" s="4"/>
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
       <c r="S25" s="4"/>
@@ -8015,22 +8116,25 @@
       <c r="IY25" s="4"/>
       <c r="IZ25" s="4"/>
       <c r="JA25" s="4"/>
+      <c r="JB25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E26" s="6"/>
-      <c r="F26" s="3"/>
+        <v>79</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F26" s="6"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
@@ -8039,10 +8143,10 @@
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
-      <c r="O26" s="6" t="n">
+      <c r="O26" s="3"/>
+      <c r="P26" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
       <c r="S26" s="4"/>
@@ -8288,22 +8392,25 @@
       <c r="IY26" s="4"/>
       <c r="IZ26" s="4"/>
       <c r="JA26" s="4"/>
+      <c r="JB26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E27" s="6"/>
-      <c r="F27" s="3"/>
+        <v>81</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F27" s="6"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
@@ -8312,10 +8419,10 @@
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
-      <c r="O27" s="6" t="n">
+      <c r="O27" s="3"/>
+      <c r="P27" s="6" t="n">
         <v>0.74</v>
       </c>
-      <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
       <c r="R27" s="4"/>
       <c r="S27" s="4"/>
@@ -8561,22 +8668,25 @@
       <c r="IY27" s="4"/>
       <c r="IZ27" s="4"/>
       <c r="JA27" s="4"/>
+      <c r="JB27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="3"/>
+        <v>83</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F28" s="6"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
@@ -8585,10 +8695,10 @@
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
-      <c r="O28" s="6" t="n">
+      <c r="O28" s="3"/>
+      <c r="P28" s="6" t="n">
         <v>0.73</v>
       </c>
-      <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
       <c r="R28" s="4"/>
       <c r="S28" s="4"/>
@@ -8834,22 +8944,25 @@
       <c r="IY28" s="4"/>
       <c r="IZ28" s="4"/>
       <c r="JA28" s="4"/>
+      <c r="JB28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E29" s="6"/>
-      <c r="F29" s="3"/>
+        <v>85</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F29" s="6"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
@@ -8858,10 +8971,10 @@
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
-      <c r="O29" s="6" t="n">
+      <c r="O29" s="3"/>
+      <c r="P29" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
       <c r="R29" s="4"/>
       <c r="S29" s="4"/>
@@ -9107,22 +9220,25 @@
       <c r="IY29" s="4"/>
       <c r="IZ29" s="4"/>
       <c r="JA29" s="4"/>
+      <c r="JB29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E30" s="6"/>
-      <c r="F30" s="3"/>
+        <v>87</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F30" s="6"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
@@ -9131,10 +9247,10 @@
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
-      <c r="O30" s="6" t="n">
+      <c r="O30" s="3"/>
+      <c r="P30" s="6" t="n">
         <v>1.8</v>
       </c>
-      <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
       <c r="R30" s="4"/>
       <c r="S30" s="4"/>
@@ -9380,22 +9496,25 @@
       <c r="IY30" s="4"/>
       <c r="IZ30" s="4"/>
       <c r="JA30" s="4"/>
+      <c r="JB30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E31" s="6"/>
-      <c r="F31" s="3"/>
+        <v>89</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F31" s="6"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
@@ -9404,10 +9523,10 @@
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
-      <c r="O31" s="6" t="n">
+      <c r="O31" s="3"/>
+      <c r="P31" s="6" t="n">
         <v>1.6</v>
       </c>
-      <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
       <c r="R31" s="4"/>
       <c r="S31" s="4"/>
@@ -9653,22 +9772,25 @@
       <c r="IY31" s="4"/>
       <c r="IZ31" s="4"/>
       <c r="JA31" s="4"/>
+      <c r="JB31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E32" s="6"/>
-      <c r="F32" s="3"/>
+        <v>91</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F32" s="6"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
@@ -9677,10 +9799,10 @@
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
-      <c r="O32" s="6" t="n">
+      <c r="O32" s="3"/>
+      <c r="P32" s="6" t="n">
         <v>1.2</v>
       </c>
-      <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
       <c r="R32" s="4"/>
       <c r="S32" s="4"/>
@@ -9926,22 +10048,25 @@
       <c r="IY32" s="4"/>
       <c r="IZ32" s="4"/>
       <c r="JA32" s="4"/>
+      <c r="JB32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E33" s="6"/>
-      <c r="F33" s="3"/>
+        <v>93</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F33" s="6"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -9950,10 +10075,10 @@
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
-      <c r="O33" s="6" t="n">
+      <c r="O33" s="3"/>
+      <c r="P33" s="6" t="n">
         <v>1.1</v>
       </c>
-      <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
       <c r="R33" s="4"/>
       <c r="S33" s="4"/>
@@ -10199,22 +10324,25 @@
       <c r="IY33" s="4"/>
       <c r="IZ33" s="4"/>
       <c r="JA33" s="4"/>
+      <c r="JB33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E34" s="6"/>
-      <c r="F34" s="3"/>
+        <v>95</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F34" s="6"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
@@ -10223,10 +10351,10 @@
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
-      <c r="O34" s="6" t="n">
+      <c r="O34" s="3"/>
+      <c r="P34" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="P34" s="4"/>
       <c r="Q34" s="4"/>
       <c r="R34" s="4"/>
       <c r="S34" s="4"/>
@@ -10472,22 +10600,25 @@
       <c r="IY34" s="4"/>
       <c r="IZ34" s="4"/>
       <c r="JA34" s="4"/>
+      <c r="JB34" s="4"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E35" s="6"/>
-      <c r="F35" s="3"/>
+        <v>97</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F35" s="6"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
@@ -10496,10 +10627,10 @@
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
-      <c r="O35" s="6" t="n">
+      <c r="O35" s="3"/>
+      <c r="P35" s="6" t="n">
         <v>1.6</v>
       </c>
-      <c r="P35" s="4"/>
       <c r="Q35" s="4"/>
       <c r="R35" s="4"/>
       <c r="S35" s="4"/>
@@ -10745,22 +10876,25 @@
       <c r="IY35" s="4"/>
       <c r="IZ35" s="4"/>
       <c r="JA35" s="4"/>
+      <c r="JB35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E36" s="6"/>
-      <c r="F36" s="3"/>
+        <v>99</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F36" s="6"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
@@ -10769,10 +10903,10 @@
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
-      <c r="O36" s="6" t="n">
+      <c r="O36" s="3"/>
+      <c r="P36" s="6" t="n">
         <v>1.6</v>
       </c>
-      <c r="P36" s="4"/>
       <c r="Q36" s="4"/>
       <c r="R36" s="4"/>
       <c r="S36" s="4"/>
@@ -11018,22 +11152,25 @@
       <c r="IY36" s="4"/>
       <c r="IZ36" s="4"/>
       <c r="JA36" s="4"/>
+      <c r="JB36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E37" s="6"/>
-      <c r="F37" s="3"/>
+        <v>101</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F37" s="6"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
@@ -11042,10 +11179,10 @@
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
-      <c r="O37" s="6" t="n">
+      <c r="O37" s="3"/>
+      <c r="P37" s="6" t="n">
         <v>1.7</v>
       </c>
-      <c r="P37" s="4"/>
       <c r="Q37" s="4"/>
       <c r="R37" s="4"/>
       <c r="S37" s="4"/>
@@ -11291,22 +11428,25 @@
       <c r="IY37" s="4"/>
       <c r="IZ37" s="4"/>
       <c r="JA37" s="4"/>
+      <c r="JB37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E38" s="6"/>
-      <c r="F38" s="3"/>
+        <v>103</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F38" s="6"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
@@ -11315,10 +11455,10 @@
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
-      <c r="O38" s="6" t="n">
+      <c r="O38" s="3"/>
+      <c r="P38" s="6" t="n">
         <v>1.1</v>
       </c>
-      <c r="P38" s="4"/>
       <c r="Q38" s="4"/>
       <c r="R38" s="4"/>
       <c r="S38" s="4"/>
@@ -11564,22 +11704,25 @@
       <c r="IY38" s="4"/>
       <c r="IZ38" s="4"/>
       <c r="JA38" s="4"/>
+      <c r="JB38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E39" s="6"/>
-      <c r="F39" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F39" s="6"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
@@ -11588,10 +11731,10 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-      <c r="O39" s="6" t="n">
+      <c r="O39" s="3"/>
+      <c r="P39" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="P39" s="4"/>
       <c r="Q39" s="4"/>
       <c r="R39" s="4"/>
       <c r="S39" s="4"/>
@@ -11837,22 +11980,25 @@
       <c r="IY39" s="4"/>
       <c r="IZ39" s="4"/>
       <c r="JA39" s="4"/>
+      <c r="JB39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E40" s="6"/>
-      <c r="F40" s="3"/>
+        <v>107</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F40" s="6"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
@@ -11861,10 +12007,10 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-      <c r="O40" s="6" t="n">
+      <c r="O40" s="3"/>
+      <c r="P40" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="P40" s="4"/>
       <c r="Q40" s="4"/>
       <c r="R40" s="4"/>
       <c r="S40" s="4"/>
@@ -12110,22 +12256,25 @@
       <c r="IY40" s="4"/>
       <c r="IZ40" s="4"/>
       <c r="JA40" s="4"/>
+      <c r="JB40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E41" s="6"/>
-      <c r="F41" s="3"/>
+        <v>109</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="F41" s="6"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -12134,10 +12283,10 @@
       <c r="L41" s="3"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
-      <c r="O41" s="6" t="n">
+      <c r="O41" s="3"/>
+      <c r="P41" s="6" t="n">
         <v>1.9</v>
       </c>
-      <c r="P41" s="4"/>
       <c r="Q41" s="4"/>
       <c r="R41" s="4"/>
       <c r="S41" s="4"/>
@@ -12383,22 +12532,25 @@
       <c r="IY41" s="4"/>
       <c r="IZ41" s="4"/>
       <c r="JA41" s="4"/>
+      <c r="JB41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E42" s="6"/>
-      <c r="F42" s="3"/>
+        <v>111</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F42" s="6"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
@@ -12407,10 +12559,10 @@
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
-      <c r="O42" s="6" t="n">
+      <c r="O42" s="3"/>
+      <c r="P42" s="6" t="n">
         <v>1.8</v>
       </c>
-      <c r="P42" s="4"/>
       <c r="Q42" s="4"/>
       <c r="R42" s="4"/>
       <c r="S42" s="4"/>
@@ -12656,22 +12808,25 @@
       <c r="IY42" s="4"/>
       <c r="IZ42" s="4"/>
       <c r="JA42" s="4"/>
+      <c r="JB42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E43" s="6"/>
-      <c r="F43" s="3"/>
+        <v>113</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F43" s="6"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
@@ -12680,10 +12835,10 @@
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
-      <c r="O43" s="6" t="n">
+      <c r="O43" s="3"/>
+      <c r="P43" s="6" t="n">
         <v>2.2</v>
       </c>
-      <c r="P43" s="4"/>
       <c r="Q43" s="4"/>
       <c r="R43" s="4"/>
       <c r="S43" s="4"/>
@@ -12929,22 +13084,25 @@
       <c r="IY43" s="4"/>
       <c r="IZ43" s="4"/>
       <c r="JA43" s="4"/>
+      <c r="JB43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E44" s="6"/>
-      <c r="F44" s="3"/>
+        <v>115</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F44" s="6"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
@@ -12953,10 +13111,10 @@
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
-      <c r="O44" s="6" t="n">
+      <c r="O44" s="3"/>
+      <c r="P44" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="P44" s="4"/>
       <c r="Q44" s="4"/>
       <c r="R44" s="4"/>
       <c r="S44" s="4"/>
@@ -13202,22 +13360,25 @@
       <c r="IY44" s="4"/>
       <c r="IZ44" s="4"/>
       <c r="JA44" s="4"/>
+      <c r="JB44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E45" s="6"/>
-      <c r="F45" s="3"/>
+        <v>117</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F45" s="6"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
@@ -13226,10 +13387,10 @@
       <c r="L45" s="3"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
-      <c r="O45" s="6" t="n">
+      <c r="O45" s="3"/>
+      <c r="P45" s="6" t="n">
         <v>3.3</v>
       </c>
-      <c r="P45" s="4"/>
       <c r="Q45" s="4"/>
       <c r="R45" s="4"/>
       <c r="S45" s="4"/>
@@ -13475,22 +13636,25 @@
       <c r="IY45" s="4"/>
       <c r="IZ45" s="4"/>
       <c r="JA45" s="4"/>
+      <c r="JB45" s="4"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E46" s="6"/>
-      <c r="F46" s="3"/>
+        <v>119</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F46" s="6"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
@@ -13499,10 +13663,10 @@
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
-      <c r="O46" s="6" t="n">
+      <c r="O46" s="3"/>
+      <c r="P46" s="6" t="n">
         <v>1.9</v>
       </c>
-      <c r="P46" s="4"/>
       <c r="Q46" s="4"/>
       <c r="R46" s="4"/>
       <c r="S46" s="4"/>
@@ -13748,22 +13912,25 @@
       <c r="IY46" s="4"/>
       <c r="IZ46" s="4"/>
       <c r="JA46" s="4"/>
+      <c r="JB46" s="4"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E47" s="6"/>
-      <c r="F47" s="3"/>
+        <v>121</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F47" s="6"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
@@ -13772,10 +13939,10 @@
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
-      <c r="O47" s="6" t="n">
+      <c r="O47" s="3"/>
+      <c r="P47" s="6" t="n">
         <v>2.1</v>
       </c>
-      <c r="P47" s="4"/>
       <c r="Q47" s="4"/>
       <c r="R47" s="4"/>
       <c r="S47" s="4"/>
@@ -14021,22 +14188,25 @@
       <c r="IY47" s="4"/>
       <c r="IZ47" s="4"/>
       <c r="JA47" s="4"/>
+      <c r="JB47" s="4"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E48" s="6"/>
-      <c r="F48" s="3"/>
+        <v>123</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F48" s="6"/>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
@@ -14045,10 +14215,10 @@
       <c r="L48" s="3"/>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
-      <c r="O48" s="6" t="n">
+      <c r="O48" s="3"/>
+      <c r="P48" s="6" t="n">
         <v>5.6</v>
       </c>
-      <c r="P48" s="4"/>
       <c r="Q48" s="4"/>
       <c r="R48" s="4"/>
       <c r="S48" s="4"/>
@@ -14294,22 +14464,25 @@
       <c r="IY48" s="4"/>
       <c r="IZ48" s="4"/>
       <c r="JA48" s="4"/>
+      <c r="JB48" s="4"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E49" s="6"/>
-      <c r="F49" s="3"/>
+        <v>125</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="F49" s="6"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
@@ -14318,10 +14491,10 @@
       <c r="L49" s="3"/>
       <c r="M49" s="3"/>
       <c r="N49" s="3"/>
-      <c r="O49" s="6" t="n">
+      <c r="O49" s="3"/>
+      <c r="P49" s="6" t="n">
         <v>7.5</v>
       </c>
-      <c r="P49" s="4"/>
       <c r="Q49" s="4"/>
       <c r="R49" s="4"/>
       <c r="S49" s="4"/>
@@ -14567,22 +14740,25 @@
       <c r="IY49" s="4"/>
       <c r="IZ49" s="4"/>
       <c r="JA49" s="4"/>
+      <c r="JB49" s="4"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="E50" s="6"/>
-      <c r="F50" s="3"/>
+        <v>127</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="F50" s="6"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
@@ -14591,10 +14767,10 @@
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
-      <c r="O50" s="6" t="n">
+      <c r="O50" s="3"/>
+      <c r="P50" s="6" t="n">
         <v>1.4</v>
       </c>
-      <c r="P50" s="4"/>
       <c r="Q50" s="4"/>
       <c r="R50" s="4"/>
       <c r="S50" s="4"/>
@@ -14840,22 +15016,25 @@
       <c r="IY50" s="4"/>
       <c r="IZ50" s="4"/>
       <c r="JA50" s="4"/>
+      <c r="JB50" s="4"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="E51" s="6"/>
-      <c r="F51" s="3"/>
+        <v>129</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="F51" s="6"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
@@ -14864,10 +15043,10 @@
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
-      <c r="O51" s="6" t="n">
+      <c r="O51" s="3"/>
+      <c r="P51" s="6" t="n">
         <v>1.9</v>
       </c>
-      <c r="P51" s="4"/>
       <c r="Q51" s="4"/>
       <c r="R51" s="4"/>
       <c r="S51" s="4"/>
@@ -15113,22 +15292,25 @@
       <c r="IY51" s="4"/>
       <c r="IZ51" s="4"/>
       <c r="JA51" s="4"/>
+      <c r="JB51" s="4"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="E52" s="6"/>
-      <c r="F52" s="3"/>
+        <v>131</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="F52" s="6"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
@@ -15137,10 +15319,10 @@
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
       <c r="N52" s="3"/>
-      <c r="O52" s="6" t="n">
+      <c r="O52" s="3"/>
+      <c r="P52" s="6" t="n">
         <v>3.1</v>
       </c>
-      <c r="P52" s="4"/>
       <c r="Q52" s="4"/>
       <c r="R52" s="4"/>
       <c r="S52" s="4"/>
@@ -15386,22 +15568,25 @@
       <c r="IY52" s="4"/>
       <c r="IZ52" s="4"/>
       <c r="JA52" s="4"/>
+      <c r="JB52" s="4"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E53" s="6"/>
-      <c r="F53" s="3"/>
+        <v>133</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F53" s="6"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
@@ -15410,10 +15595,10 @@
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
-      <c r="O53" s="6" t="n">
+      <c r="O53" s="3"/>
+      <c r="P53" s="6" t="n">
         <v>2.5</v>
       </c>
-      <c r="P53" s="4"/>
       <c r="Q53" s="4"/>
       <c r="R53" s="4"/>
       <c r="S53" s="4"/>
@@ -15659,22 +15844,25 @@
       <c r="IY53" s="4"/>
       <c r="IZ53" s="4"/>
       <c r="JA53" s="4"/>
+      <c r="JB53" s="4"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="E54" s="6"/>
-      <c r="F54" s="3"/>
+        <v>135</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F54" s="6"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
@@ -15683,10 +15871,10 @@
       <c r="L54" s="3"/>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
-      <c r="O54" s="6" t="n">
+      <c r="O54" s="3"/>
+      <c r="P54" s="6" t="n">
         <v>4.4</v>
       </c>
-      <c r="P54" s="4"/>
       <c r="Q54" s="4"/>
       <c r="R54" s="4"/>
       <c r="S54" s="4"/>
@@ -15932,22 +16120,25 @@
       <c r="IY54" s="4"/>
       <c r="IZ54" s="4"/>
       <c r="JA54" s="4"/>
+      <c r="JB54" s="4"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="E55" s="6"/>
-      <c r="F55" s="3"/>
+        <v>137</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="F55" s="6"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
@@ -15956,10 +16147,10 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-      <c r="O55" s="6" t="n">
+      <c r="O55" s="3"/>
+      <c r="P55" s="6" t="n">
         <v>0.3</v>
       </c>
-      <c r="P55" s="4"/>
       <c r="Q55" s="4"/>
       <c r="R55" s="4"/>
       <c r="S55" s="4"/>
@@ -16205,22 +16396,25 @@
       <c r="IY55" s="4"/>
       <c r="IZ55" s="4"/>
       <c r="JA55" s="4"/>
+      <c r="JB55" s="4"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="E56" s="6"/>
-      <c r="F56" s="3"/>
+        <v>139</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="F56" s="6"/>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
@@ -16229,10 +16423,10 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-      <c r="O56" s="6" t="n">
+      <c r="O56" s="3"/>
+      <c r="P56" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="P56" s="4"/>
       <c r="Q56" s="4"/>
       <c r="R56" s="4"/>
       <c r="S56" s="4"/>
@@ -16478,22 +16672,25 @@
       <c r="IY56" s="4"/>
       <c r="IZ56" s="4"/>
       <c r="JA56" s="4"/>
+      <c r="JB56" s="4"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E57" s="6"/>
-      <c r="F57" s="3"/>
+        <v>141</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="F57" s="6"/>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
@@ -16502,10 +16699,10 @@
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
       <c r="N57" s="3"/>
-      <c r="O57" s="6" t="n">
+      <c r="O57" s="3"/>
+      <c r="P57" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="P57" s="4"/>
       <c r="Q57" s="4"/>
       <c r="R57" s="4"/>
       <c r="S57" s="4"/>
@@ -16751,22 +16948,25 @@
       <c r="IY57" s="4"/>
       <c r="IZ57" s="4"/>
       <c r="JA57" s="4"/>
+      <c r="JB57" s="4"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E58" s="6"/>
-      <c r="F58" s="3"/>
+        <v>143</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F58" s="6"/>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
@@ -16775,10 +16975,10 @@
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
-      <c r="O58" s="6" t="n">
+      <c r="O58" s="3"/>
+      <c r="P58" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="P58" s="4"/>
       <c r="Q58" s="4"/>
       <c r="R58" s="4"/>
       <c r="S58" s="4"/>
@@ -17024,22 +17224,25 @@
       <c r="IY58" s="4"/>
       <c r="IZ58" s="4"/>
       <c r="JA58" s="4"/>
+      <c r="JB58" s="4"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="E59" s="6"/>
-      <c r="F59" s="3"/>
+        <v>145</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F59" s="6"/>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
@@ -17048,10 +17251,10 @@
       <c r="L59" s="3"/>
       <c r="M59" s="3"/>
       <c r="N59" s="3"/>
-      <c r="O59" s="6" t="n">
+      <c r="O59" s="3"/>
+      <c r="P59" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="P59" s="4"/>
       <c r="Q59" s="4"/>
       <c r="R59" s="4"/>
       <c r="S59" s="4"/>
@@ -17297,22 +17500,25 @@
       <c r="IY59" s="4"/>
       <c r="IZ59" s="4"/>
       <c r="JA59" s="4"/>
+      <c r="JB59" s="4"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="E60" s="6"/>
-      <c r="F60" s="3"/>
+        <v>147</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="F60" s="6"/>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
@@ -17321,10 +17527,10 @@
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
       <c r="N60" s="3"/>
-      <c r="O60" s="6" t="n">
+      <c r="O60" s="3"/>
+      <c r="P60" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="P60" s="4"/>
       <c r="Q60" s="4"/>
       <c r="R60" s="4"/>
       <c r="S60" s="4"/>
@@ -17570,22 +17776,25 @@
       <c r="IY60" s="4"/>
       <c r="IZ60" s="4"/>
       <c r="JA60" s="4"/>
+      <c r="JB60" s="4"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="E61" s="6"/>
-      <c r="F61" s="3"/>
+        <v>149</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F61" s="6"/>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
@@ -17594,10 +17803,10 @@
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
       <c r="N61" s="3"/>
-      <c r="O61" s="6" t="n">
+      <c r="O61" s="3"/>
+      <c r="P61" s="6" t="n">
         <v>0.7</v>
       </c>
-      <c r="P61" s="4"/>
       <c r="Q61" s="4"/>
       <c r="R61" s="4"/>
       <c r="S61" s="4"/>
@@ -17843,22 +18052,25 @@
       <c r="IY61" s="4"/>
       <c r="IZ61" s="4"/>
       <c r="JA61" s="4"/>
+      <c r="JB61" s="4"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E62" s="6"/>
-      <c r="F62" s="3"/>
+        <v>151</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F62" s="6"/>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
@@ -17867,10 +18079,10 @@
       <c r="L62" s="3"/>
       <c r="M62" s="3"/>
       <c r="N62" s="3"/>
-      <c r="O62" s="6" t="n">
+      <c r="O62" s="3"/>
+      <c r="P62" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="P62" s="4"/>
       <c r="Q62" s="4"/>
       <c r="R62" s="4"/>
       <c r="S62" s="4"/>
@@ -18116,22 +18328,25 @@
       <c r="IY62" s="4"/>
       <c r="IZ62" s="4"/>
       <c r="JA62" s="4"/>
+      <c r="JB62" s="4"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E63" s="6"/>
-      <c r="F63" s="3"/>
+        <v>153</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F63" s="6"/>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
@@ -18140,8 +18355,8 @@
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
       <c r="N63" s="3"/>
-      <c r="O63" s="6"/>
-      <c r="P63" s="4"/>
+      <c r="O63" s="3"/>
+      <c r="P63" s="6"/>
       <c r="Q63" s="4"/>
       <c r="R63" s="4"/>
       <c r="S63" s="4"/>
@@ -18387,22 +18602,25 @@
       <c r="IY63" s="4"/>
       <c r="IZ63" s="4"/>
       <c r="JA63" s="4"/>
+      <c r="JB63" s="4"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="n">
         <v>2903710000</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="E64" s="6"/>
-      <c r="F64" s="3"/>
+        <v>156</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F64" s="6"/>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
@@ -18411,10 +18629,10 @@
       <c r="L64" s="3"/>
       <c r="M64" s="3"/>
       <c r="N64" s="3"/>
-      <c r="O64" s="6" t="n">
+      <c r="O64" s="3"/>
+      <c r="P64" s="6" t="n">
         <v>0.055</v>
       </c>
-      <c r="P64" s="4"/>
       <c r="Q64" s="4"/>
       <c r="R64" s="4"/>
       <c r="S64" s="4"/>
@@ -18660,22 +18878,25 @@
       <c r="IY64" s="4"/>
       <c r="IZ64" s="4"/>
       <c r="JA64" s="4"/>
+      <c r="JB64" s="4"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E65" s="6"/>
-      <c r="F65" s="3"/>
+        <v>158</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F65" s="6"/>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
@@ -18684,10 +18905,10 @@
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
       <c r="N65" s="3"/>
-      <c r="O65" s="6" t="n">
+      <c r="O65" s="3"/>
+      <c r="P65" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="P65" s="4"/>
       <c r="Q65" s="4"/>
       <c r="R65" s="4"/>
       <c r="S65" s="4"/>
@@ -18933,22 +19154,25 @@
       <c r="IY65" s="4"/>
       <c r="IZ65" s="4"/>
       <c r="JA65" s="4"/>
+      <c r="JB65" s="4"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="E66" s="6"/>
-      <c r="F66" s="3"/>
+        <v>160</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="F66" s="6"/>
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
@@ -18957,10 +19181,10 @@
       <c r="L66" s="3"/>
       <c r="M66" s="3"/>
       <c r="N66" s="3"/>
-      <c r="O66" s="6" t="n">
+      <c r="O66" s="3"/>
+      <c r="P66" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="P66" s="4"/>
       <c r="Q66" s="4"/>
       <c r="R66" s="4"/>
       <c r="S66" s="4"/>
@@ -19206,22 +19430,25 @@
       <c r="IY66" s="4"/>
       <c r="IZ66" s="4"/>
       <c r="JA66" s="4"/>
+      <c r="JB66" s="4"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="E67" s="6"/>
-      <c r="F67" s="3"/>
+        <v>162</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F67" s="6"/>
       <c r="G67" s="3"/>
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
@@ -19230,10 +19457,10 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-      <c r="O67" s="6" t="n">
+      <c r="O67" s="3"/>
+      <c r="P67" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="P67" s="4"/>
       <c r="Q67" s="4"/>
       <c r="R67" s="4"/>
       <c r="S67" s="4"/>
@@ -19479,22 +19706,25 @@
       <c r="IY67" s="4"/>
       <c r="IZ67" s="4"/>
       <c r="JA67" s="4"/>
+      <c r="JB67" s="4"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="E68" s="6"/>
-      <c r="F68" s="3"/>
+        <v>164</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="F68" s="6"/>
       <c r="G68" s="3"/>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
@@ -19503,10 +19733,10 @@
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
-      <c r="O68" s="6" t="n">
+      <c r="O68" s="3"/>
+      <c r="P68" s="6" t="n">
         <v>0.08</v>
       </c>
-      <c r="P68" s="4"/>
       <c r="Q68" s="4"/>
       <c r="R68" s="4"/>
       <c r="S68" s="4"/>
@@ -19752,22 +19982,25 @@
       <c r="IY68" s="4"/>
       <c r="IZ68" s="4"/>
       <c r="JA68" s="4"/>
+      <c r="JB68" s="4"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="n">
         <v>2903720010</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="E69" s="6"/>
-      <c r="F69" s="3"/>
+        <v>167</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="F69" s="6"/>
       <c r="G69" s="3"/>
       <c r="H69" s="3"/>
       <c r="I69" s="3"/>
@@ -19776,10 +20009,10 @@
       <c r="L69" s="3"/>
       <c r="M69" s="3"/>
       <c r="N69" s="3"/>
-      <c r="O69" s="6" t="n">
+      <c r="O69" s="3"/>
+      <c r="P69" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="P69" s="4"/>
       <c r="Q69" s="4"/>
       <c r="R69" s="4"/>
       <c r="S69" s="4"/>
@@ -20025,22 +20258,25 @@
       <c r="IY69" s="4"/>
       <c r="IZ69" s="4"/>
       <c r="JA69" s="4"/>
+      <c r="JB69" s="4"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="n">
         <v>2903720090</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E70" s="6"/>
-      <c r="F70" s="3"/>
+        <v>170</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F70" s="6"/>
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
@@ -20049,10 +20285,10 @@
       <c r="L70" s="3"/>
       <c r="M70" s="3"/>
       <c r="N70" s="3"/>
-      <c r="O70" s="6" t="n">
+      <c r="O70" s="3"/>
+      <c r="P70" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="P70" s="4"/>
       <c r="Q70" s="4"/>
       <c r="R70" s="4"/>
       <c r="S70" s="4"/>
@@ -20298,22 +20534,25 @@
       <c r="IY70" s="4"/>
       <c r="IZ70" s="4"/>
       <c r="JA70" s="4"/>
+      <c r="JB70" s="4"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="E71" s="6"/>
-      <c r="F71" s="3"/>
+        <v>172</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="F71" s="6"/>
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
@@ -20322,10 +20561,10 @@
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
       <c r="N71" s="3"/>
-      <c r="O71" s="6" t="n">
+      <c r="O71" s="3"/>
+      <c r="P71" s="6" t="n">
         <v>0.022</v>
       </c>
-      <c r="P71" s="4"/>
       <c r="Q71" s="4"/>
       <c r="R71" s="4"/>
       <c r="S71" s="4"/>
@@ -20571,22 +20810,25 @@
       <c r="IY71" s="4"/>
       <c r="IZ71" s="4"/>
       <c r="JA71" s="4"/>
+      <c r="JB71" s="4"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="E72" s="6"/>
-      <c r="F72" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F72" s="6"/>
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
@@ -20595,10 +20837,10 @@
       <c r="L72" s="3"/>
       <c r="M72" s="3"/>
       <c r="N72" s="3"/>
-      <c r="O72" s="6" t="n">
+      <c r="O72" s="3"/>
+      <c r="P72" s="6" t="n">
         <v>0.022</v>
       </c>
-      <c r="P72" s="4"/>
       <c r="Q72" s="4"/>
       <c r="R72" s="4"/>
       <c r="S72" s="4"/>
@@ -20844,22 +21086,25 @@
       <c r="IY72" s="4"/>
       <c r="IZ72" s="4"/>
       <c r="JA72" s="4"/>
+      <c r="JB72" s="4"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="E73" s="6"/>
-      <c r="F73" s="3"/>
+        <v>176</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F73" s="6"/>
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
@@ -20868,10 +21113,10 @@
       <c r="L73" s="3"/>
       <c r="M73" s="3"/>
       <c r="N73" s="3"/>
-      <c r="O73" s="6" t="n">
+      <c r="O73" s="3"/>
+      <c r="P73" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="P73" s="4"/>
       <c r="Q73" s="4"/>
       <c r="R73" s="4"/>
       <c r="S73" s="4"/>
@@ -21117,22 +21362,25 @@
       <c r="IY73" s="4"/>
       <c r="IZ73" s="4"/>
       <c r="JA73" s="4"/>
+      <c r="JB73" s="4"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="E74" s="6"/>
-      <c r="F74" s="3"/>
+        <v>178</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="F74" s="6"/>
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
@@ -21141,10 +21389,10 @@
       <c r="L74" s="3"/>
       <c r="M74" s="3"/>
       <c r="N74" s="3"/>
-      <c r="O74" s="6" t="n">
+      <c r="O74" s="3"/>
+      <c r="P74" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="P74" s="4"/>
       <c r="Q74" s="4"/>
       <c r="R74" s="4"/>
       <c r="S74" s="4"/>
@@ -21390,22 +21638,25 @@
       <c r="IY74" s="4"/>
       <c r="IZ74" s="4"/>
       <c r="JA74" s="4"/>
+      <c r="JB74" s="4"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="E75" s="6"/>
-      <c r="F75" s="3"/>
+        <v>180</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="F75" s="6"/>
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
@@ -21414,10 +21665,10 @@
       <c r="L75" s="3"/>
       <c r="M75" s="3"/>
       <c r="N75" s="3"/>
-      <c r="O75" s="6" t="n">
+      <c r="O75" s="3"/>
+      <c r="P75" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="P75" s="4"/>
       <c r="Q75" s="4"/>
       <c r="R75" s="4"/>
       <c r="S75" s="4"/>
@@ -21663,22 +21914,25 @@
       <c r="IY75" s="4"/>
       <c r="IZ75" s="4"/>
       <c r="JA75" s="4"/>
+      <c r="JB75" s="4"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="E76" s="6"/>
-      <c r="F76" s="3"/>
+        <v>182</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F76" s="6"/>
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
@@ -21687,10 +21941,10 @@
       <c r="L76" s="3"/>
       <c r="M76" s="3"/>
       <c r="N76" s="3"/>
-      <c r="O76" s="6" t="n">
+      <c r="O76" s="3"/>
+      <c r="P76" s="6" t="n">
         <v>0.06</v>
       </c>
-      <c r="P76" s="4"/>
       <c r="Q76" s="4"/>
       <c r="R76" s="4"/>
       <c r="S76" s="4"/>
@@ -21936,22 +22190,25 @@
       <c r="IY76" s="4"/>
       <c r="IZ76" s="4"/>
       <c r="JA76" s="4"/>
+      <c r="JB76" s="4"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="n">
         <v>2903730000</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="E77" s="6"/>
-      <c r="F77" s="3"/>
+        <v>185</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F77" s="6"/>
       <c r="G77" s="3"/>
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
@@ -21960,10 +22217,10 @@
       <c r="L77" s="3"/>
       <c r="M77" s="3"/>
       <c r="N77" s="3"/>
-      <c r="O77" s="6" t="n">
+      <c r="O77" s="3"/>
+      <c r="P77" s="6" t="n">
         <v>0.07</v>
       </c>
-      <c r="P77" s="4"/>
       <c r="Q77" s="4"/>
       <c r="R77" s="4"/>
       <c r="S77" s="4"/>
@@ -22209,22 +22466,25 @@
       <c r="IY77" s="4"/>
       <c r="IZ77" s="4"/>
       <c r="JA77" s="4"/>
+      <c r="JB77" s="4"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="n">
         <v>2903730000</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="E78" s="6"/>
-      <c r="F78" s="3"/>
+        <v>187</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="F78" s="6"/>
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
@@ -22233,10 +22493,10 @@
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
       <c r="N78" s="3"/>
-      <c r="O78" s="6" t="n">
+      <c r="O78" s="3"/>
+      <c r="P78" s="6" t="n">
         <v>0.11</v>
       </c>
-      <c r="P78" s="4"/>
       <c r="Q78" s="4"/>
       <c r="R78" s="4"/>
       <c r="S78" s="4"/>
@@ -22482,22 +22742,25 @@
       <c r="IY78" s="4"/>
       <c r="IZ78" s="4"/>
       <c r="JA78" s="4"/>
+      <c r="JB78" s="4"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="n">
         <v>2903740000</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E79" s="6"/>
-      <c r="F79" s="3"/>
+        <v>190</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="F79" s="6"/>
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
@@ -22506,10 +22769,10 @@
       <c r="L79" s="3"/>
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
-      <c r="O79" s="6" t="n">
+      <c r="O79" s="3"/>
+      <c r="P79" s="6" t="n">
         <v>0.07</v>
       </c>
-      <c r="P79" s="4"/>
       <c r="Q79" s="4"/>
       <c r="R79" s="4"/>
       <c r="S79" s="4"/>
@@ -22755,22 +23018,25 @@
       <c r="IY79" s="4"/>
       <c r="IZ79" s="4"/>
       <c r="JA79" s="4"/>
+      <c r="JB79" s="4"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5" t="n">
         <v>2903740000</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="E80" s="6"/>
-      <c r="F80" s="3"/>
+        <v>192</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F80" s="6"/>
       <c r="G80" s="3"/>
       <c r="H80" s="3"/>
       <c r="I80" s="3"/>
@@ -22779,10 +23045,10 @@
       <c r="L80" s="3"/>
       <c r="M80" s="3"/>
       <c r="N80" s="3"/>
-      <c r="O80" s="6" t="n">
+      <c r="O80" s="3"/>
+      <c r="P80" s="6" t="n">
         <v>0.065</v>
       </c>
-      <c r="P80" s="4"/>
       <c r="Q80" s="4"/>
       <c r="R80" s="4"/>
       <c r="S80" s="4"/>
@@ -23028,22 +23294,25 @@
       <c r="IY80" s="4"/>
       <c r="IZ80" s="4"/>
       <c r="JA80" s="4"/>
+      <c r="JB80" s="4"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="E81" s="6"/>
-      <c r="F81" s="3"/>
+        <v>194</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F81" s="6"/>
       <c r="G81" s="3"/>
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
@@ -23052,10 +23321,10 @@
       <c r="L81" s="3"/>
       <c r="M81" s="3"/>
       <c r="N81" s="3"/>
-      <c r="O81" s="6" t="n">
+      <c r="O81" s="3"/>
+      <c r="P81" s="6" t="n">
         <v>0.005</v>
       </c>
-      <c r="P81" s="4"/>
       <c r="Q81" s="4"/>
       <c r="R81" s="4"/>
       <c r="S81" s="4"/>
@@ -23301,22 +23570,25 @@
       <c r="IY81" s="4"/>
       <c r="IZ81" s="4"/>
       <c r="JA81" s="4"/>
+      <c r="JB81" s="4"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="E82" s="6"/>
-      <c r="F82" s="3"/>
+        <v>196</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="F82" s="6"/>
       <c r="G82" s="3"/>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
@@ -23325,10 +23597,10 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-      <c r="O82" s="6" t="n">
+      <c r="O82" s="3"/>
+      <c r="P82" s="6" t="n">
         <v>0.07</v>
       </c>
-      <c r="P82" s="4"/>
       <c r="Q82" s="4"/>
       <c r="R82" s="4"/>
       <c r="S82" s="4"/>
@@ -23574,22 +23846,25 @@
       <c r="IY82" s="4"/>
       <c r="IZ82" s="4"/>
       <c r="JA82" s="4"/>
+      <c r="JB82" s="4"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E83" s="6"/>
-      <c r="F83" s="3"/>
+        <v>198</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F83" s="6"/>
       <c r="G83" s="3"/>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
@@ -23598,10 +23873,10 @@
       <c r="L83" s="3"/>
       <c r="M83" s="3"/>
       <c r="N83" s="3"/>
-      <c r="O83" s="6" t="n">
+      <c r="O83" s="3"/>
+      <c r="P83" s="6" t="n">
         <v>0.09</v>
       </c>
-      <c r="P83" s="4"/>
       <c r="Q83" s="4"/>
       <c r="R83" s="4"/>
       <c r="S83" s="4"/>
@@ -23847,22 +24122,25 @@
       <c r="IY83" s="4"/>
       <c r="IZ83" s="4"/>
       <c r="JA83" s="4"/>
+      <c r="JB83" s="4"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="E84" s="6"/>
-      <c r="F84" s="3"/>
+        <v>200</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="F84" s="6"/>
       <c r="G84" s="3"/>
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
@@ -23871,10 +24149,10 @@
       <c r="L84" s="3"/>
       <c r="M84" s="3"/>
       <c r="N84" s="3"/>
-      <c r="O84" s="6" t="n">
+      <c r="O84" s="3"/>
+      <c r="P84" s="6" t="n">
         <v>0.08</v>
       </c>
-      <c r="P84" s="4"/>
       <c r="Q84" s="4"/>
       <c r="R84" s="4"/>
       <c r="S84" s="4"/>
@@ -24120,22 +24398,25 @@
       <c r="IY84" s="4"/>
       <c r="IZ84" s="4"/>
       <c r="JA84" s="4"/>
+      <c r="JB84" s="4"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="E85" s="6"/>
-      <c r="F85" s="3"/>
+        <v>202</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F85" s="6"/>
       <c r="G85" s="3"/>
       <c r="H85" s="3"/>
       <c r="I85" s="3"/>
@@ -24144,10 +24425,10 @@
       <c r="L85" s="3"/>
       <c r="M85" s="3"/>
       <c r="N85" s="3"/>
-      <c r="O85" s="6" t="n">
+      <c r="O85" s="3"/>
+      <c r="P85" s="6" t="n">
         <v>0.09</v>
       </c>
-      <c r="P85" s="4"/>
       <c r="Q85" s="4"/>
       <c r="R85" s="4"/>
       <c r="S85" s="4"/>
@@ -24393,22 +24674,25 @@
       <c r="IY85" s="4"/>
       <c r="IZ85" s="4"/>
       <c r="JA85" s="4"/>
+      <c r="JB85" s="4"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="5" t="n">
         <v>2903750000</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E86" s="6"/>
-      <c r="F86" s="3"/>
+        <v>205</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F86" s="6"/>
       <c r="G86" s="3"/>
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
@@ -24417,10 +24701,10 @@
       <c r="L86" s="3"/>
       <c r="M86" s="3"/>
       <c r="N86" s="3"/>
-      <c r="O86" s="6" t="n">
+      <c r="O86" s="3"/>
+      <c r="P86" s="6" t="n">
         <v>0.07</v>
       </c>
-      <c r="P86" s="4"/>
       <c r="Q86" s="4"/>
       <c r="R86" s="4"/>
       <c r="S86" s="4"/>
@@ -24666,22 +24950,25 @@
       <c r="IY86" s="4"/>
       <c r="IZ86" s="4"/>
       <c r="JA86" s="4"/>
+      <c r="JB86" s="4"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="5" t="n">
         <v>2903750000</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="E87" s="6"/>
-      <c r="F87" s="3"/>
+        <v>207</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F87" s="6"/>
       <c r="G87" s="3"/>
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
@@ -24690,10 +24977,10 @@
       <c r="L87" s="3"/>
       <c r="M87" s="3"/>
       <c r="N87" s="3"/>
-      <c r="O87" s="6" t="n">
+      <c r="O87" s="3"/>
+      <c r="P87" s="6" t="n">
         <v>0.025</v>
       </c>
-      <c r="P87" s="4"/>
       <c r="Q87" s="4"/>
       <c r="R87" s="4"/>
       <c r="S87" s="4"/>
@@ -24939,22 +25226,25 @@
       <c r="IY87" s="4"/>
       <c r="IZ87" s="4"/>
       <c r="JA87" s="4"/>
+      <c r="JB87" s="4"/>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="5" t="n">
         <v>2903750000</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="E88" s="6"/>
-      <c r="F88" s="3"/>
+        <v>209</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F88" s="6"/>
       <c r="G88" s="3"/>
       <c r="H88" s="3"/>
       <c r="I88" s="3"/>
@@ -24963,10 +25253,10 @@
       <c r="L88" s="3"/>
       <c r="M88" s="3"/>
       <c r="N88" s="3"/>
-      <c r="O88" s="6" t="n">
+      <c r="O88" s="3"/>
+      <c r="P88" s="6" t="n">
         <v>0.033</v>
       </c>
-      <c r="P88" s="4"/>
       <c r="Q88" s="4"/>
       <c r="R88" s="4"/>
       <c r="S88" s="4"/>
@@ -25212,22 +25502,25 @@
       <c r="IY88" s="4"/>
       <c r="IZ88" s="4"/>
       <c r="JA88" s="4"/>
+      <c r="JB88" s="4"/>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="E89" s="6"/>
-      <c r="F89" s="3"/>
+        <v>210</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F89" s="6"/>
       <c r="G89" s="3"/>
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
@@ -25236,10 +25529,10 @@
       <c r="L89" s="3"/>
       <c r="M89" s="3"/>
       <c r="N89" s="3"/>
-      <c r="O89" s="6" t="n">
+      <c r="O89" s="3"/>
+      <c r="P89" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="P89" s="4"/>
       <c r="Q89" s="4"/>
       <c r="R89" s="4"/>
       <c r="S89" s="4"/>
@@ -25485,22 +25778,25 @@
       <c r="IY89" s="4"/>
       <c r="IZ89" s="4"/>
       <c r="JA89" s="4"/>
+      <c r="JB89" s="4"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="E90" s="6"/>
-      <c r="F90" s="3"/>
+        <v>212</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F90" s="6"/>
       <c r="G90" s="3"/>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
@@ -25509,10 +25805,10 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-      <c r="O90" s="6" t="n">
+      <c r="O90" s="3"/>
+      <c r="P90" s="6" t="n">
         <v>0.9</v>
       </c>
-      <c r="P90" s="4"/>
       <c r="Q90" s="4"/>
       <c r="R90" s="4"/>
       <c r="S90" s="4"/>
@@ -25758,22 +26054,25 @@
       <c r="IY90" s="4"/>
       <c r="IZ90" s="4"/>
       <c r="JA90" s="4"/>
+      <c r="JB90" s="4"/>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="E91" s="6"/>
-      <c r="F91" s="3"/>
+        <v>214</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="F91" s="6"/>
       <c r="G91" s="3"/>
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
@@ -25782,10 +26081,10 @@
       <c r="L91" s="3"/>
       <c r="M91" s="3"/>
       <c r="N91" s="3"/>
-      <c r="O91" s="6" t="n">
+      <c r="O91" s="3"/>
+      <c r="P91" s="6" t="n">
         <v>0.1</v>
       </c>
-      <c r="P91" s="4"/>
       <c r="Q91" s="4"/>
       <c r="R91" s="4"/>
       <c r="S91" s="4"/>
@@ -26031,22 +26330,25 @@
       <c r="IY91" s="4"/>
       <c r="IZ91" s="4"/>
       <c r="JA91" s="4"/>
+      <c r="JB91" s="4"/>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="E92" s="6"/>
-      <c r="F92" s="3"/>
+        <v>216</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F92" s="6"/>
       <c r="G92" s="3"/>
       <c r="H92" s="3"/>
       <c r="I92" s="3"/>
@@ -26055,10 +26357,10 @@
       <c r="L92" s="3"/>
       <c r="M92" s="3"/>
       <c r="N92" s="3"/>
-      <c r="O92" s="6" t="n">
+      <c r="O92" s="3"/>
+      <c r="P92" s="6" t="n">
         <v>0.23</v>
       </c>
-      <c r="P92" s="4"/>
       <c r="Q92" s="4"/>
       <c r="R92" s="4"/>
       <c r="S92" s="4"/>
@@ -26304,22 +26606,25 @@
       <c r="IY92" s="4"/>
       <c r="IZ92" s="4"/>
       <c r="JA92" s="4"/>
+      <c r="JB92" s="4"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="E93" s="6"/>
-      <c r="F93" s="3"/>
+        <v>218</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="F93" s="6"/>
       <c r="G93" s="3"/>
       <c r="H93" s="3"/>
       <c r="I93" s="3"/>
@@ -26328,10 +26633,10 @@
       <c r="L93" s="3"/>
       <c r="M93" s="3"/>
       <c r="N93" s="3"/>
-      <c r="O93" s="6" t="n">
+      <c r="O93" s="3"/>
+      <c r="P93" s="6" t="n">
         <v>0.28</v>
       </c>
-      <c r="P93" s="4"/>
       <c r="Q93" s="4"/>
       <c r="R93" s="4"/>
       <c r="S93" s="4"/>
@@ -26577,22 +26882,25 @@
       <c r="IY93" s="4"/>
       <c r="IZ93" s="4"/>
       <c r="JA93" s="4"/>
+      <c r="JB93" s="4"/>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="E94" s="6"/>
-      <c r="F94" s="3"/>
+        <v>220</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F94" s="6"/>
       <c r="G94" s="3"/>
       <c r="H94" s="3"/>
       <c r="I94" s="3"/>
@@ -26601,10 +26909,10 @@
       <c r="L94" s="3"/>
       <c r="M94" s="3"/>
       <c r="N94" s="3"/>
-      <c r="O94" s="6" t="n">
+      <c r="O94" s="3"/>
+      <c r="P94" s="6" t="n">
         <v>0.52</v>
       </c>
-      <c r="P94" s="4"/>
       <c r="Q94" s="4"/>
       <c r="R94" s="4"/>
       <c r="S94" s="4"/>
@@ -26850,22 +27158,25 @@
       <c r="IY94" s="4"/>
       <c r="IZ94" s="4"/>
       <c r="JA94" s="4"/>
+      <c r="JB94" s="4"/>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="E95" s="6"/>
-      <c r="F95" s="3"/>
+        <v>222</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="F95" s="6"/>
       <c r="G95" s="3"/>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>
@@ -26874,10 +27185,10 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-      <c r="O95" s="6" t="n">
+      <c r="O95" s="3"/>
+      <c r="P95" s="6" t="n">
         <v>0.09</v>
       </c>
-      <c r="P95" s="4"/>
       <c r="Q95" s="4"/>
       <c r="R95" s="4"/>
       <c r="S95" s="4"/>
@@ -27123,22 +27434,25 @@
       <c r="IY95" s="4"/>
       <c r="IZ95" s="4"/>
       <c r="JA95" s="4"/>
+      <c r="JB95" s="4"/>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="E96" s="6"/>
-      <c r="F96" s="3"/>
+        <v>224</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="F96" s="6"/>
       <c r="G96" s="3"/>
       <c r="H96" s="3"/>
       <c r="I96" s="3"/>
@@ -27147,10 +27461,10 @@
       <c r="L96" s="3"/>
       <c r="M96" s="3"/>
       <c r="N96" s="3"/>
-      <c r="O96" s="6" t="n">
+      <c r="O96" s="3"/>
+      <c r="P96" s="6" t="n">
         <v>0.13</v>
       </c>
-      <c r="P96" s="4"/>
       <c r="Q96" s="4"/>
       <c r="R96" s="4"/>
       <c r="S96" s="4"/>
@@ -27396,22 +27710,25 @@
       <c r="IY96" s="4"/>
       <c r="IZ96" s="4"/>
       <c r="JA96" s="4"/>
+      <c r="JB96" s="4"/>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="E97" s="6"/>
-      <c r="F97" s="3"/>
+        <v>226</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="F97" s="6"/>
       <c r="G97" s="3"/>
       <c r="H97" s="3"/>
       <c r="I97" s="3"/>
@@ -27420,10 +27737,10 @@
       <c r="L97" s="3"/>
       <c r="M97" s="3"/>
       <c r="N97" s="3"/>
-      <c r="O97" s="6" t="n">
+      <c r="O97" s="3"/>
+      <c r="P97" s="6" t="n">
         <v>0.12</v>
       </c>
-      <c r="P97" s="4"/>
       <c r="Q97" s="4"/>
       <c r="R97" s="4"/>
       <c r="S97" s="4"/>
@@ -27669,22 +27986,25 @@
       <c r="IY97" s="4"/>
       <c r="IZ97" s="4"/>
       <c r="JA97" s="4"/>
+      <c r="JB97" s="4"/>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="E98" s="6"/>
-      <c r="F98" s="3"/>
+        <v>228</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F98" s="6"/>
       <c r="G98" s="3"/>
       <c r="H98" s="3"/>
       <c r="I98" s="3"/>
@@ -27693,10 +28013,10 @@
       <c r="L98" s="3"/>
       <c r="M98" s="3"/>
       <c r="N98" s="3"/>
-      <c r="O98" s="6" t="n">
+      <c r="O98" s="3"/>
+      <c r="P98" s="6" t="n">
         <v>0.14</v>
       </c>
-      <c r="P98" s="4"/>
       <c r="Q98" s="4"/>
       <c r="R98" s="4"/>
       <c r="S98" s="4"/>
@@ -27942,22 +28262,25 @@
       <c r="IY98" s="4"/>
       <c r="IZ98" s="4"/>
       <c r="JA98" s="4"/>
+      <c r="JB98" s="4"/>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="E99" s="6"/>
-      <c r="F99" s="3"/>
+        <v>230</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="F99" s="6"/>
       <c r="G99" s="3"/>
       <c r="H99" s="3"/>
       <c r="I99" s="3"/>
@@ -27966,10 +28289,10 @@
       <c r="L99" s="3"/>
       <c r="M99" s="3"/>
       <c r="N99" s="3"/>
-      <c r="O99" s="6" t="n">
+      <c r="O99" s="3"/>
+      <c r="P99" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="P99" s="4"/>
       <c r="Q99" s="4"/>
       <c r="R99" s="4"/>
       <c r="S99" s="4"/>
@@ -28215,22 +28538,25 @@
       <c r="IY99" s="4"/>
       <c r="IZ99" s="4"/>
       <c r="JA99" s="4"/>
+      <c r="JB99" s="4"/>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="E100" s="6"/>
-      <c r="F100" s="3"/>
+        <v>232</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="F100" s="6"/>
       <c r="G100" s="3"/>
       <c r="H100" s="3"/>
       <c r="I100" s="3"/>
@@ -28239,10 +28565,10 @@
       <c r="L100" s="3"/>
       <c r="M100" s="3"/>
       <c r="N100" s="3"/>
-      <c r="O100" s="6" t="n">
+      <c r="O100" s="3"/>
+      <c r="P100" s="6" t="n">
         <v>0.04</v>
       </c>
-      <c r="P100" s="4"/>
       <c r="Q100" s="4"/>
       <c r="R100" s="4"/>
       <c r="S100" s="4"/>
@@ -28488,22 +28814,25 @@
       <c r="IY100" s="4"/>
       <c r="IZ100" s="4"/>
       <c r="JA100" s="4"/>
+      <c r="JB100" s="4"/>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="E101" s="6"/>
-      <c r="F101" s="3"/>
+        <v>234</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="F101" s="6"/>
       <c r="G101" s="3"/>
       <c r="H101" s="3"/>
       <c r="I101" s="3"/>
@@ -28512,10 +28841,10 @@
       <c r="L101" s="3"/>
       <c r="M101" s="3"/>
       <c r="N101" s="3"/>
-      <c r="O101" s="6" t="n">
+      <c r="O101" s="3"/>
+      <c r="P101" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="P101" s="4"/>
       <c r="Q101" s="4"/>
       <c r="R101" s="4"/>
       <c r="S101" s="4"/>
@@ -28761,22 +29090,25 @@
       <c r="IY101" s="4"/>
       <c r="IZ101" s="4"/>
       <c r="JA101" s="4"/>
+      <c r="JB101" s="4"/>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="E102" s="6"/>
-      <c r="F102" s="3"/>
+        <v>236</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="F102" s="6"/>
       <c r="G102" s="3"/>
       <c r="H102" s="3"/>
       <c r="I102" s="3"/>
@@ -28785,10 +29117,10 @@
       <c r="L102" s="3"/>
       <c r="M102" s="3"/>
       <c r="N102" s="3"/>
-      <c r="O102" s="6" t="n">
+      <c r="O102" s="3"/>
+      <c r="P102" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="P102" s="4"/>
       <c r="Q102" s="4"/>
       <c r="R102" s="4"/>
       <c r="S102" s="4"/>
@@ -29034,22 +29366,25 @@
       <c r="IY102" s="4"/>
       <c r="IZ102" s="4"/>
       <c r="JA102" s="4"/>
+      <c r="JB102" s="4"/>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="E103" s="6"/>
-      <c r="F103" s="3"/>
+        <v>238</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="F103" s="6"/>
       <c r="G103" s="3"/>
       <c r="H103" s="3"/>
       <c r="I103" s="3"/>
@@ -29058,10 +29393,10 @@
       <c r="L103" s="3"/>
       <c r="M103" s="3"/>
       <c r="N103" s="3"/>
-      <c r="O103" s="6" t="n">
+      <c r="O103" s="3"/>
+      <c r="P103" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="P103" s="4"/>
       <c r="Q103" s="4"/>
       <c r="R103" s="4"/>
       <c r="S103" s="4"/>
@@ -29307,22 +29642,25 @@
       <c r="IY103" s="4"/>
       <c r="IZ103" s="4"/>
       <c r="JA103" s="4"/>
+      <c r="JB103" s="4"/>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="5" t="n">
         <v>2903793090</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="E104" s="6"/>
-      <c r="F104" s="3"/>
+        <v>240</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="F104" s="6"/>
       <c r="G104" s="3"/>
       <c r="H104" s="3"/>
       <c r="I104" s="3"/>
@@ -29331,10 +29669,10 @@
       <c r="L104" s="3"/>
       <c r="M104" s="3"/>
       <c r="N104" s="3"/>
-      <c r="O104" s="6" t="n">
+      <c r="O104" s="3"/>
+      <c r="P104" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="P104" s="4"/>
       <c r="Q104" s="4"/>
       <c r="R104" s="4"/>
       <c r="S104" s="4"/>
@@ -29580,22 +29918,25 @@
       <c r="IY104" s="4"/>
       <c r="IZ104" s="4"/>
       <c r="JA104" s="4"/>
+      <c r="JB104" s="4"/>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="5" t="n">
         <v>2903793020</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="E105" s="6"/>
-      <c r="F105" s="3"/>
+        <v>242</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="F105" s="6"/>
       <c r="G105" s="3"/>
       <c r="H105" s="3"/>
       <c r="I105" s="3"/>
@@ -29604,10 +29945,10 @@
       <c r="L105" s="3"/>
       <c r="M105" s="3"/>
       <c r="N105" s="3"/>
-      <c r="O105" s="6" t="n">
+      <c r="O105" s="3"/>
+      <c r="P105" s="6" t="n">
         <v>0.12</v>
       </c>
-      <c r="P105" s="4"/>
       <c r="Q105" s="4"/>
       <c r="R105" s="4"/>
       <c r="S105" s="4"/>
@@ -29853,22 +30194,25 @@
       <c r="IY105" s="4"/>
       <c r="IZ105" s="4"/>
       <c r="JA105" s="4"/>
+      <c r="JB105" s="4"/>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="9" t="n">
         <v>2845901000</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E106" s="6"/>
-      <c r="F106" s="3"/>
+      <c r="E106" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F106" s="6"/>
       <c r="G106" s="3"/>
       <c r="H106" s="3"/>
       <c r="I106" s="3"/>
@@ -29877,8 +30221,8 @@
       <c r="L106" s="3"/>
       <c r="M106" s="3"/>
       <c r="N106" s="3"/>
-      <c r="O106" s="6"/>
-      <c r="P106" s="4"/>
+      <c r="O106" s="3"/>
+      <c r="P106" s="6"/>
       <c r="Q106" s="4"/>
       <c r="R106" s="4"/>
       <c r="S106" s="4"/>
@@ -30124,22 +30468,25 @@
       <c r="IY106" s="4"/>
       <c r="IZ106" s="4"/>
       <c r="JA106" s="4"/>
+      <c r="JB106" s="4"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="9" t="n">
         <v>2845901000</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E107" s="6"/>
-      <c r="F107" s="3"/>
+      <c r="E107" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F107" s="6"/>
       <c r="G107" s="3"/>
       <c r="H107" s="3"/>
       <c r="I107" s="3"/>
@@ -30148,8 +30495,8 @@
       <c r="L107" s="3"/>
       <c r="M107" s="3"/>
       <c r="N107" s="3"/>
-      <c r="O107" s="6"/>
-      <c r="P107" s="4"/>
+      <c r="O107" s="3"/>
+      <c r="P107" s="6"/>
       <c r="Q107" s="4"/>
       <c r="R107" s="4"/>
       <c r="S107" s="4"/>
@@ -30395,19 +30742,23 @@
       <c r="IY107" s="4"/>
       <c r="IZ107" s="4"/>
       <c r="JA107" s="4"/>
+      <c r="JB107" s="4"/>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="9" t="n">
         <v>2845901000</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>11</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30415,13 +30766,16 @@
         <v>2845901000</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>14</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30429,13 +30783,16 @@
         <v>2845901000</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>16</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30443,13 +30800,16 @@
         <v>2845901000</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>18</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30457,13 +30817,16 @@
         <v>2845901000</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>20</v>
+      </c>
+      <c r="E112" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30471,13 +30834,16 @@
         <v>2845901000</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>23</v>
+      </c>
+      <c r="E113" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30485,13 +30851,16 @@
         <v>2845901000</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>26</v>
+      </c>
+      <c r="E114" s="6" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30499,13 +30868,16 @@
         <v>2845901000</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>29</v>
+      </c>
+      <c r="E115" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30513,13 +30885,16 @@
         <v>2845901000</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>32</v>
+      </c>
+      <c r="E116" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30527,13 +30902,16 @@
         <v>2845901000</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>35</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30541,13 +30919,16 @@
         <v>2845901000</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>38</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30555,13 +30936,16 @@
         <v>2845901000</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>41</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30569,13 +30953,16 @@
         <v>2845901000</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>44</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30583,13 +30970,16 @@
         <v>2845901000</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>47</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30597,13 +30987,16 @@
         <v>2845901000</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>50</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30611,13 +31004,16 @@
         <v>2845901000</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30625,13 +31021,16 @@
         <v>2845901000</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
+      </c>
+      <c r="E124" s="6" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30639,13 +31038,16 @@
         <v>2845901000</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30653,13 +31055,16 @@
         <v>2845901000</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>62</v>
+        <v>66</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30667,13 +31072,16 @@
         <v>2845901000</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30681,13 +31089,16 @@
         <v>2845901000</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>65</v>
+        <v>73</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30695,13 +31106,16 @@
         <v>2845901000</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>69</v>
+        <v>76</v>
+      </c>
+      <c r="E129" s="6" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30709,13 +31123,16 @@
         <v>2845901000</v>
       </c>
       <c r="B130" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>72</v>
+        <v>79</v>
+      </c>
+      <c r="E130" s="6" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30723,13 +31140,16 @@
         <v>2845901000</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>74</v>
+        <v>81</v>
+      </c>
+      <c r="E131" s="6" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30737,13 +31157,16 @@
         <v>2845901000</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>76</v>
+        <v>83</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30751,13 +31174,16 @@
         <v>2845901000</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>78</v>
+        <v>85</v>
+      </c>
+      <c r="E133" s="6" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30765,13 +31191,16 @@
         <v>2845901000</v>
       </c>
       <c r="B134" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>80</v>
+        <v>87</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30779,13 +31208,16 @@
         <v>2845901000</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>82</v>
+        <v>89</v>
+      </c>
+      <c r="E135" s="6" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30793,13 +31225,16 @@
         <v>2845901000</v>
       </c>
       <c r="B136" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>84</v>
+        <v>91</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30807,13 +31242,16 @@
         <v>2845901000</v>
       </c>
       <c r="B137" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>86</v>
+        <v>93</v>
+      </c>
+      <c r="E137" s="6" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30821,13 +31259,16 @@
         <v>2845901000</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>88</v>
+        <v>95</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30835,13 +31276,16 @@
         <v>2845901000</v>
       </c>
       <c r="B139" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>90</v>
+        <v>97</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30849,13 +31293,16 @@
         <v>2845901000</v>
       </c>
       <c r="B140" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>92</v>
+        <v>99</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30863,13 +31310,16 @@
         <v>2845901000</v>
       </c>
       <c r="B141" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>94</v>
+        <v>101</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30877,13 +31327,16 @@
         <v>2845901000</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>96</v>
+        <v>103</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30891,13 +31344,16 @@
         <v>2845901000</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>98</v>
+        <v>105</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30905,13 +31361,16 @@
         <v>2845901000</v>
       </c>
       <c r="B144" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>100</v>
+        <v>107</v>
+      </c>
+      <c r="E144" s="6" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30919,13 +31378,16 @@
         <v>2845901000</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>102</v>
+        <v>109</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30933,13 +31395,16 @@
         <v>2845901000</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>104</v>
+        <v>111</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30947,13 +31412,16 @@
         <v>2845901000</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30961,13 +31429,16 @@
         <v>2845901000</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>108</v>
+        <v>115</v>
+      </c>
+      <c r="E148" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30975,13 +31446,16 @@
         <v>2845901000</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>110</v>
+        <v>117</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30989,13 +31463,16 @@
         <v>2845901000</v>
       </c>
       <c r="B150" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31003,13 +31480,16 @@
         <v>2845901000</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>114</v>
+        <v>121</v>
+      </c>
+      <c r="E151" s="6" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31017,13 +31497,16 @@
         <v>2845901000</v>
       </c>
       <c r="B152" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>116</v>
+        <v>123</v>
+      </c>
+      <c r="E152" s="6" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31031,13 +31514,16 @@
         <v>2845901000</v>
       </c>
       <c r="B153" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>118</v>
+        <v>125</v>
+      </c>
+      <c r="E153" s="6" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31045,13 +31531,16 @@
         <v>2845901000</v>
       </c>
       <c r="B154" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>120</v>
+        <v>127</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31059,13 +31548,16 @@
         <v>2845901000</v>
       </c>
       <c r="B155" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>122</v>
+        <v>129</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31073,13 +31565,16 @@
         <v>2845901000</v>
       </c>
       <c r="B156" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>124</v>
+        <v>131</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31087,13 +31582,16 @@
         <v>2845901000</v>
       </c>
       <c r="B157" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>126</v>
+        <v>133</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31101,13 +31599,16 @@
         <v>2845901000</v>
       </c>
       <c r="B158" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>128</v>
+        <v>135</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31115,13 +31616,16 @@
         <v>2845901000</v>
       </c>
       <c r="B159" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>130</v>
+        <v>137</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31129,13 +31633,16 @@
         <v>2845901000</v>
       </c>
       <c r="B160" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>132</v>
+        <v>139</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31143,13 +31650,16 @@
         <v>2845901000</v>
       </c>
       <c r="B161" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>134</v>
+        <v>141</v>
+      </c>
+      <c r="E161" s="6" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31157,13 +31667,16 @@
         <v>2845901000</v>
       </c>
       <c r="B162" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>136</v>
+        <v>143</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31171,13 +31684,16 @@
         <v>2845901000</v>
       </c>
       <c r="B163" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>138</v>
+        <v>145</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31185,13 +31701,16 @@
         <v>2845901000</v>
       </c>
       <c r="B164" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>140</v>
+        <v>147</v>
+      </c>
+      <c r="E164" s="6" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31199,13 +31718,16 @@
         <v>2845901000</v>
       </c>
       <c r="B165" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>142</v>
+        <v>149</v>
+      </c>
+      <c r="E165" s="6" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31213,13 +31735,16 @@
         <v>2845901000</v>
       </c>
       <c r="B166" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>144</v>
+        <v>151</v>
+      </c>
+      <c r="E166" s="6" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31227,13 +31752,16 @@
         <v>2845901000</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>149</v>
+        <v>156</v>
+      </c>
+      <c r="E167" s="6" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31241,13 +31769,16 @@
         <v>2845901000</v>
       </c>
       <c r="B168" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>151</v>
+        <v>158</v>
+      </c>
+      <c r="E168" s="6" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31255,13 +31786,16 @@
         <v>2845901000</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D169" s="6" t="s">
-        <v>153</v>
+        <v>160</v>
+      </c>
+      <c r="E169" s="6" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31269,13 +31803,16 @@
         <v>2845901000</v>
       </c>
       <c r="B170" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>155</v>
+        <v>162</v>
+      </c>
+      <c r="E170" s="6" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31283,13 +31820,16 @@
         <v>2845901000</v>
       </c>
       <c r="B171" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>157</v>
+        <v>164</v>
+      </c>
+      <c r="E171" s="6" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31297,13 +31837,16 @@
         <v>2845901000</v>
       </c>
       <c r="B172" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>160</v>
+        <v>167</v>
+      </c>
+      <c r="E172" s="6" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31311,13 +31854,16 @@
         <v>2845901000</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>163</v>
+        <v>170</v>
+      </c>
+      <c r="E173" s="6" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31325,13 +31871,16 @@
         <v>2845901000</v>
       </c>
       <c r="B174" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>165</v>
+        <v>172</v>
+      </c>
+      <c r="E174" s="6" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31339,13 +31888,16 @@
         <v>2845901000</v>
       </c>
       <c r="B175" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D175" s="6" t="s">
-        <v>167</v>
+        <v>174</v>
+      </c>
+      <c r="E175" s="6" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31353,13 +31905,16 @@
         <v>2845901000</v>
       </c>
       <c r="B176" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>169</v>
+        <v>176</v>
+      </c>
+      <c r="E176" s="6" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31367,13 +31922,16 @@
         <v>2845901000</v>
       </c>
       <c r="B177" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>171</v>
+        <v>178</v>
+      </c>
+      <c r="E177" s="6" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31381,13 +31939,16 @@
         <v>2845901000</v>
       </c>
       <c r="B178" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>173</v>
+        <v>180</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31395,13 +31956,16 @@
         <v>2845901000</v>
       </c>
       <c r="B179" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>175</v>
+        <v>182</v>
+      </c>
+      <c r="E179" s="6" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31409,13 +31973,16 @@
         <v>2845901000</v>
       </c>
       <c r="B180" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>178</v>
+        <v>185</v>
+      </c>
+      <c r="E180" s="6" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31423,13 +31990,16 @@
         <v>2845901000</v>
       </c>
       <c r="B181" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>180</v>
+        <v>187</v>
+      </c>
+      <c r="E181" s="6" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31437,13 +32007,16 @@
         <v>2845901000</v>
       </c>
       <c r="B182" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>183</v>
+        <v>190</v>
+      </c>
+      <c r="E182" s="6" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31451,13 +32024,16 @@
         <v>2845901000</v>
       </c>
       <c r="B183" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>185</v>
+        <v>192</v>
+      </c>
+      <c r="E183" s="6" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31465,13 +32041,16 @@
         <v>2845901000</v>
       </c>
       <c r="B184" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>187</v>
+        <v>194</v>
+      </c>
+      <c r="E184" s="6" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31479,13 +32058,16 @@
         <v>2845901000</v>
       </c>
       <c r="B185" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>189</v>
+        <v>196</v>
+      </c>
+      <c r="E185" s="6" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31493,13 +32075,16 @@
         <v>2845901000</v>
       </c>
       <c r="B186" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>191</v>
+        <v>198</v>
+      </c>
+      <c r="E186" s="6" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31507,13 +32092,16 @@
         <v>2845901000</v>
       </c>
       <c r="B187" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>193</v>
+        <v>200</v>
+      </c>
+      <c r="E187" s="6" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31521,13 +32109,16 @@
         <v>2845901000</v>
       </c>
       <c r="B188" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>195</v>
+        <v>202</v>
+      </c>
+      <c r="E188" s="6" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31535,13 +32126,16 @@
         <v>2845901000</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>198</v>
+        <v>205</v>
+      </c>
+      <c r="E189" s="6" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31549,13 +32143,16 @@
         <v>2845901000</v>
       </c>
       <c r="B190" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>200</v>
+        <v>207</v>
+      </c>
+      <c r="E190" s="6" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31563,13 +32160,16 @@
         <v>2845901000</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>200</v>
+        <v>209</v>
+      </c>
+      <c r="E191" s="6" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31577,13 +32177,16 @@
         <v>2845901000</v>
       </c>
       <c r="B192" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>203</v>
+        <v>210</v>
+      </c>
+      <c r="E192" s="6" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31591,13 +32194,16 @@
         <v>2845901000</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>205</v>
+        <v>212</v>
+      </c>
+      <c r="E193" s="6" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31605,13 +32211,16 @@
         <v>2845901000</v>
       </c>
       <c r="B194" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>207</v>
+        <v>214</v>
+      </c>
+      <c r="E194" s="6" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31619,13 +32228,16 @@
         <v>2845901000</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="D195" s="6" t="s">
-        <v>209</v>
+        <v>216</v>
+      </c>
+      <c r="E195" s="6" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31633,13 +32245,16 @@
         <v>2845901000</v>
       </c>
       <c r="B196" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>211</v>
+        <v>218</v>
+      </c>
+      <c r="E196" s="6" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31647,13 +32262,16 @@
         <v>2845901000</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>213</v>
+        <v>220</v>
+      </c>
+      <c r="E197" s="6" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31661,13 +32279,16 @@
         <v>2845901000</v>
       </c>
       <c r="B198" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>215</v>
+        <v>222</v>
+      </c>
+      <c r="E198" s="6" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31675,13 +32296,16 @@
         <v>2845901000</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="D199" s="6" t="s">
-        <v>217</v>
+        <v>224</v>
+      </c>
+      <c r="E199" s="6" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31689,13 +32313,16 @@
         <v>2845901000</v>
       </c>
       <c r="B200" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>219</v>
+        <v>226</v>
+      </c>
+      <c r="E200" s="6" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31703,13 +32330,16 @@
         <v>2845901000</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="D201" s="6" t="s">
-        <v>221</v>
+        <v>228</v>
+      </c>
+      <c r="E201" s="6" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31717,13 +32347,16 @@
         <v>2845901000</v>
       </c>
       <c r="B202" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>223</v>
+        <v>230</v>
+      </c>
+      <c r="E202" s="6" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31731,13 +32364,16 @@
         <v>2845901000</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="D203" s="6" t="s">
-        <v>225</v>
+        <v>232</v>
+      </c>
+      <c r="E203" s="6" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31745,13 +32381,16 @@
         <v>2845901000</v>
       </c>
       <c r="B204" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>227</v>
+        <v>234</v>
+      </c>
+      <c r="E204" s="6" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31759,13 +32398,16 @@
         <v>2845901000</v>
       </c>
       <c r="B205" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="C205" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="C205" s="6" t="s">
-        <v>228</v>
-      </c>
       <c r="D205" s="6" t="s">
-        <v>229</v>
+        <v>236</v>
+      </c>
+      <c r="E205" s="6" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31773,13 +32415,16 @@
         <v>2845901000</v>
       </c>
       <c r="B206" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>231</v>
+        <v>238</v>
+      </c>
+      <c r="E206" s="6" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31787,13 +32432,16 @@
         <v>2845901000</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>233</v>
+        <v>240</v>
+      </c>
+      <c r="E207" s="6" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31801,13 +32449,16 @@
         <v>2845901000</v>
       </c>
       <c r="B208" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C208" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="D208" s="6" t="s">
-        <v>235</v>
+        <v>242</v>
+      </c>
+      <c r="D208" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="E208" s="6" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31815,13 +32466,16 @@
         <v>2845909090</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D209" s="6" t="s">
         <v>7</v>
+      </c>
+      <c r="E209" s="6" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31829,13 +32483,16 @@
         <v>2845909090</v>
       </c>
       <c r="B210" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D210" s="6" t="s">
         <v>9</v>
+      </c>
+      <c r="E210" s="6" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31843,13 +32500,16 @@
         <v>2845909090</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D211" s="6" t="s">
         <v>11</v>
+      </c>
+      <c r="E211" s="6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31857,13 +32517,16 @@
         <v>2845909090</v>
       </c>
       <c r="B212" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D212" s="6" t="s">
         <v>14</v>
+      </c>
+      <c r="E212" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31871,13 +32534,16 @@
         <v>2845909090</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D213" s="6" t="s">
         <v>16</v>
+      </c>
+      <c r="E213" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31885,13 +32551,16 @@
         <v>2845909090</v>
       </c>
       <c r="B214" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D214" s="6" t="s">
         <v>18</v>
+      </c>
+      <c r="E214" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31899,13 +32568,16 @@
         <v>2845909090</v>
       </c>
       <c r="B215" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D215" s="6" t="s">
         <v>20</v>
+      </c>
+      <c r="E215" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31913,13 +32585,16 @@
         <v>2845909090</v>
       </c>
       <c r="B216" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D216" s="6" t="s">
         <v>23</v>
+      </c>
+      <c r="E216" s="6" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31927,13 +32602,16 @@
         <v>2845909090</v>
       </c>
       <c r="B217" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D217" s="6" t="s">
         <v>26</v>
+      </c>
+      <c r="E217" s="6" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31941,13 +32619,16 @@
         <v>2845909090</v>
       </c>
       <c r="B218" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D218" s="6" t="s">
         <v>29</v>
+      </c>
+      <c r="E218" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31955,13 +32636,16 @@
         <v>2845909090</v>
       </c>
       <c r="B219" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D219" s="6" t="s">
         <v>32</v>
+      </c>
+      <c r="E219" s="6" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31969,13 +32653,16 @@
         <v>2845909090</v>
       </c>
       <c r="B220" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D220" s="6" t="s">
         <v>35</v>
+      </c>
+      <c r="E220" s="6" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31983,13 +32670,16 @@
         <v>2845909090</v>
       </c>
       <c r="B221" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D221" s="6" t="s">
         <v>38</v>
+      </c>
+      <c r="E221" s="6" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31997,13 +32687,16 @@
         <v>2845909090</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D222" s="6" t="s">
         <v>41</v>
+      </c>
+      <c r="E222" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32011,13 +32704,16 @@
         <v>2845909090</v>
       </c>
       <c r="B223" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D223" s="6" t="s">
         <v>44</v>
+      </c>
+      <c r="E223" s="6" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32025,13 +32721,16 @@
         <v>2845909090</v>
       </c>
       <c r="B224" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D224" s="6" t="s">
         <v>47</v>
+      </c>
+      <c r="E224" s="6" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32039,13 +32738,16 @@
         <v>2845909090</v>
       </c>
       <c r="B225" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D225" s="6" t="s">
         <v>50</v>
+      </c>
+      <c r="E225" s="6" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32053,13 +32755,16 @@
         <v>2845909090</v>
       </c>
       <c r="B226" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="E226" s="6" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32067,13 +32772,16 @@
         <v>2845909090</v>
       </c>
       <c r="B227" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
+      </c>
+      <c r="E227" s="6" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32081,13 +32789,16 @@
         <v>2845909090</v>
       </c>
       <c r="B228" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
+      </c>
+      <c r="E228" s="6" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32095,13 +32806,16 @@
         <v>2845909090</v>
       </c>
       <c r="B229" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D229" s="6" t="s">
-        <v>62</v>
+        <v>66</v>
+      </c>
+      <c r="E229" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32109,13 +32823,16 @@
         <v>2845909090</v>
       </c>
       <c r="B230" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
+      </c>
+      <c r="E230" s="6" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32123,13 +32840,16 @@
         <v>2845909090</v>
       </c>
       <c r="B231" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>65</v>
+        <v>73</v>
+      </c>
+      <c r="E231" s="6" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32137,13 +32857,16 @@
         <v>2845909090</v>
       </c>
       <c r="B232" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>69</v>
+        <v>76</v>
+      </c>
+      <c r="E232" s="6" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32151,13 +32874,16 @@
         <v>2845909090</v>
       </c>
       <c r="B233" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>72</v>
+        <v>79</v>
+      </c>
+      <c r="E233" s="6" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32165,13 +32891,16 @@
         <v>2845909090</v>
       </c>
       <c r="B234" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>74</v>
+        <v>81</v>
+      </c>
+      <c r="E234" s="6" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32179,13 +32908,16 @@
         <v>2845909090</v>
       </c>
       <c r="B235" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>76</v>
+        <v>83</v>
+      </c>
+      <c r="E235" s="6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32193,13 +32925,16 @@
         <v>2845909090</v>
       </c>
       <c r="B236" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D236" s="6" t="s">
-        <v>78</v>
+        <v>85</v>
+      </c>
+      <c r="E236" s="6" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32207,13 +32942,16 @@
         <v>2845909090</v>
       </c>
       <c r="B237" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>80</v>
+        <v>87</v>
+      </c>
+      <c r="E237" s="6" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32221,13 +32959,16 @@
         <v>2845909090</v>
       </c>
       <c r="B238" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>82</v>
+        <v>89</v>
+      </c>
+      <c r="E238" s="6" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32235,13 +32976,16 @@
         <v>2845909090</v>
       </c>
       <c r="B239" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>84</v>
+        <v>91</v>
+      </c>
+      <c r="E239" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32249,13 +32993,16 @@
         <v>2845909090</v>
       </c>
       <c r="B240" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>86</v>
+        <v>93</v>
+      </c>
+      <c r="E240" s="6" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32263,13 +33010,16 @@
         <v>2845909090</v>
       </c>
       <c r="B241" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>88</v>
+        <v>95</v>
+      </c>
+      <c r="E241" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32277,13 +33027,16 @@
         <v>2845909090</v>
       </c>
       <c r="B242" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>90</v>
+        <v>97</v>
+      </c>
+      <c r="E242" s="6" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32291,13 +33044,16 @@
         <v>2845909090</v>
       </c>
       <c r="B243" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>92</v>
+        <v>99</v>
+      </c>
+      <c r="E243" s="6" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32305,13 +33061,16 @@
         <v>2845909090</v>
       </c>
       <c r="B244" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>94</v>
+        <v>101</v>
+      </c>
+      <c r="E244" s="6" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32319,13 +33078,16 @@
         <v>2845909090</v>
       </c>
       <c r="B245" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>96</v>
+        <v>103</v>
+      </c>
+      <c r="E245" s="6" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32333,13 +33095,16 @@
         <v>2845909090</v>
       </c>
       <c r="B246" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>98</v>
+        <v>105</v>
+      </c>
+      <c r="E246" s="6" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32347,13 +33112,16 @@
         <v>2845909090</v>
       </c>
       <c r="B247" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>100</v>
+        <v>107</v>
+      </c>
+      <c r="E247" s="6" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32361,13 +33129,16 @@
         <v>2845909090</v>
       </c>
       <c r="B248" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>102</v>
+        <v>109</v>
+      </c>
+      <c r="E248" s="6" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32375,13 +33146,16 @@
         <v>2845909090</v>
       </c>
       <c r="B249" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D249" s="6" t="s">
-        <v>104</v>
+        <v>111</v>
+      </c>
+      <c r="E249" s="6" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32389,13 +33163,16 @@
         <v>2845909090</v>
       </c>
       <c r="B250" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D250" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
+      </c>
+      <c r="E250" s="6" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32403,13 +33180,16 @@
         <v>2845909090</v>
       </c>
       <c r="B251" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="D251" s="6" t="s">
-        <v>108</v>
+        <v>115</v>
+      </c>
+      <c r="E251" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32417,13 +33197,16 @@
         <v>2845909090</v>
       </c>
       <c r="B252" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D252" s="6" t="s">
-        <v>110</v>
+        <v>117</v>
+      </c>
+      <c r="E252" s="6" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32431,13 +33214,16 @@
         <v>2845909090</v>
       </c>
       <c r="B253" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D253" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
+      </c>
+      <c r="E253" s="6" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32445,13 +33231,16 @@
         <v>2845909090</v>
       </c>
       <c r="B254" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D254" s="6" t="s">
-        <v>114</v>
+        <v>121</v>
+      </c>
+      <c r="E254" s="6" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32459,13 +33248,16 @@
         <v>2845909090</v>
       </c>
       <c r="B255" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D255" s="6" t="s">
-        <v>116</v>
+        <v>123</v>
+      </c>
+      <c r="E255" s="6" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32473,13 +33265,16 @@
         <v>2845909090</v>
       </c>
       <c r="B256" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>118</v>
+        <v>125</v>
+      </c>
+      <c r="E256" s="6" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32487,13 +33282,16 @@
         <v>2845909090</v>
       </c>
       <c r="B257" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="D257" s="6" t="s">
-        <v>120</v>
+        <v>127</v>
+      </c>
+      <c r="E257" s="6" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32501,13 +33299,16 @@
         <v>2845909090</v>
       </c>
       <c r="B258" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D258" s="6" t="s">
-        <v>122</v>
+        <v>129</v>
+      </c>
+      <c r="E258" s="6" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32515,13 +33316,16 @@
         <v>2845909090</v>
       </c>
       <c r="B259" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D259" s="6" t="s">
-        <v>124</v>
+        <v>131</v>
+      </c>
+      <c r="E259" s="6" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32529,13 +33333,16 @@
         <v>2845909090</v>
       </c>
       <c r="B260" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="D260" s="6" t="s">
-        <v>126</v>
+        <v>133</v>
+      </c>
+      <c r="E260" s="6" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32543,13 +33350,16 @@
         <v>2845909090</v>
       </c>
       <c r="B261" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D261" s="6" t="s">
-        <v>128</v>
+        <v>135</v>
+      </c>
+      <c r="E261" s="6" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32557,13 +33367,16 @@
         <v>2845909090</v>
       </c>
       <c r="B262" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D262" s="6" t="s">
-        <v>130</v>
+        <v>137</v>
+      </c>
+      <c r="E262" s="6" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32571,13 +33384,16 @@
         <v>2845909090</v>
       </c>
       <c r="B263" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="D263" s="6" t="s">
-        <v>132</v>
+        <v>139</v>
+      </c>
+      <c r="E263" s="6" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32585,13 +33401,16 @@
         <v>2845909090</v>
       </c>
       <c r="B264" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D264" s="6" t="s">
-        <v>134</v>
+        <v>141</v>
+      </c>
+      <c r="E264" s="6" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32599,13 +33418,16 @@
         <v>2845909090</v>
       </c>
       <c r="B265" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D265" s="6" t="s">
-        <v>136</v>
+        <v>143</v>
+      </c>
+      <c r="E265" s="6" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32613,13 +33435,16 @@
         <v>2845909090</v>
       </c>
       <c r="B266" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="D266" s="6" t="s">
-        <v>138</v>
+        <v>145</v>
+      </c>
+      <c r="E266" s="6" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32627,13 +33452,16 @@
         <v>2845909090</v>
       </c>
       <c r="B267" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D267" s="6" t="s">
-        <v>140</v>
+        <v>147</v>
+      </c>
+      <c r="E267" s="6" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32641,13 +33469,16 @@
         <v>2845909090</v>
       </c>
       <c r="B268" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="D268" s="6" t="s">
-        <v>142</v>
+        <v>149</v>
+      </c>
+      <c r="E268" s="6" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32655,13 +33486,16 @@
         <v>2845909090</v>
       </c>
       <c r="B269" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D269" s="6" t="s">
-        <v>144</v>
+        <v>151</v>
+      </c>
+      <c r="E269" s="6" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32669,13 +33503,16 @@
         <v>2845909090</v>
       </c>
       <c r="B270" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="D270" s="6" t="s">
-        <v>149</v>
+        <v>156</v>
+      </c>
+      <c r="E270" s="6" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32683,13 +33520,16 @@
         <v>2845909090</v>
       </c>
       <c r="B271" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="D271" s="6" t="s">
-        <v>151</v>
+        <v>158</v>
+      </c>
+      <c r="E271" s="6" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32697,13 +33537,16 @@
         <v>2845909090</v>
       </c>
       <c r="B272" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D272" s="6" t="s">
-        <v>153</v>
+        <v>160</v>
+      </c>
+      <c r="E272" s="6" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32711,13 +33554,16 @@
         <v>2845909090</v>
       </c>
       <c r="B273" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="D273" s="6" t="s">
-        <v>155</v>
+        <v>162</v>
+      </c>
+      <c r="E273" s="6" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32725,13 +33571,16 @@
         <v>2845909090</v>
       </c>
       <c r="B274" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="D274" s="6" t="s">
-        <v>157</v>
+        <v>164</v>
+      </c>
+      <c r="E274" s="6" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32739,13 +33588,16 @@
         <v>2845909090</v>
       </c>
       <c r="B275" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D275" s="6" t="s">
-        <v>160</v>
+        <v>167</v>
+      </c>
+      <c r="E275" s="6" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32753,13 +33605,16 @@
         <v>2845909090</v>
       </c>
       <c r="B276" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="D276" s="6" t="s">
-        <v>163</v>
+        <v>170</v>
+      </c>
+      <c r="E276" s="6" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32767,13 +33622,16 @@
         <v>2845909090</v>
       </c>
       <c r="B277" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="D277" s="6" t="s">
-        <v>165</v>
+        <v>172</v>
+      </c>
+      <c r="E277" s="6" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32781,13 +33639,16 @@
         <v>2845909090</v>
       </c>
       <c r="B278" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D278" s="6" t="s">
-        <v>167</v>
+        <v>174</v>
+      </c>
+      <c r="E278" s="6" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32795,13 +33656,16 @@
         <v>2845909090</v>
       </c>
       <c r="B279" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D279" s="6" t="s">
-        <v>169</v>
+        <v>176</v>
+      </c>
+      <c r="E279" s="6" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32809,13 +33673,16 @@
         <v>2845909090</v>
       </c>
       <c r="B280" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="D280" s="6" t="s">
-        <v>171</v>
+        <v>178</v>
+      </c>
+      <c r="E280" s="6" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32823,13 +33690,16 @@
         <v>2845909090</v>
       </c>
       <c r="B281" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="D281" s="6" t="s">
-        <v>173</v>
+        <v>180</v>
+      </c>
+      <c r="E281" s="6" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32837,13 +33707,16 @@
         <v>2845909090</v>
       </c>
       <c r="B282" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="D282" s="6" t="s">
-        <v>175</v>
+        <v>182</v>
+      </c>
+      <c r="E282" s="6" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32851,13 +33724,16 @@
         <v>2845909090</v>
       </c>
       <c r="B283" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="D283" s="6" t="s">
-        <v>178</v>
+        <v>185</v>
+      </c>
+      <c r="E283" s="6" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32865,13 +33741,16 @@
         <v>2845909090</v>
       </c>
       <c r="B284" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="D284" s="6" t="s">
-        <v>180</v>
+        <v>187</v>
+      </c>
+      <c r="E284" s="6" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32879,13 +33758,16 @@
         <v>2845909090</v>
       </c>
       <c r="B285" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="D285" s="6" t="s">
-        <v>183</v>
+        <v>190</v>
+      </c>
+      <c r="E285" s="6" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32893,13 +33775,16 @@
         <v>2845909090</v>
       </c>
       <c r="B286" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="D286" s="6" t="s">
-        <v>185</v>
+        <v>192</v>
+      </c>
+      <c r="E286" s="6" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32907,13 +33792,16 @@
         <v>2845909090</v>
       </c>
       <c r="B287" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="D287" s="6" t="s">
-        <v>187</v>
+        <v>194</v>
+      </c>
+      <c r="E287" s="6" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32921,13 +33809,16 @@
         <v>2845909090</v>
       </c>
       <c r="B288" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D288" s="6" t="s">
-        <v>189</v>
+        <v>196</v>
+      </c>
+      <c r="E288" s="6" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32935,13 +33826,16 @@
         <v>2845909090</v>
       </c>
       <c r="B289" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D289" s="6" t="s">
-        <v>191</v>
+        <v>198</v>
+      </c>
+      <c r="E289" s="6" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32949,13 +33843,16 @@
         <v>2845909090</v>
       </c>
       <c r="B290" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="D290" s="6" t="s">
-        <v>193</v>
+        <v>200</v>
+      </c>
+      <c r="E290" s="6" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32963,13 +33860,16 @@
         <v>2845909090</v>
       </c>
       <c r="B291" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="D291" s="6" t="s">
-        <v>195</v>
+        <v>202</v>
+      </c>
+      <c r="E291" s="6" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32977,13 +33877,16 @@
         <v>2845909090</v>
       </c>
       <c r="B292" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D292" s="6" t="s">
-        <v>198</v>
+        <v>205</v>
+      </c>
+      <c r="E292" s="6" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32991,13 +33894,16 @@
         <v>2845909090</v>
       </c>
       <c r="B293" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="D293" s="6" t="s">
-        <v>200</v>
+        <v>207</v>
+      </c>
+      <c r="E293" s="6" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33005,13 +33911,16 @@
         <v>2845909090</v>
       </c>
       <c r="B294" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D294" s="6" t="s">
-        <v>200</v>
+        <v>209</v>
+      </c>
+      <c r="E294" s="6" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33019,13 +33928,16 @@
         <v>2845909090</v>
       </c>
       <c r="B295" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D295" s="6" t="s">
-        <v>203</v>
+        <v>210</v>
+      </c>
+      <c r="E295" s="6" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33033,13 +33945,16 @@
         <v>2845909090</v>
       </c>
       <c r="B296" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="D296" s="6" t="s">
-        <v>205</v>
+        <v>212</v>
+      </c>
+      <c r="E296" s="6" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33047,13 +33962,16 @@
         <v>2845909090</v>
       </c>
       <c r="B297" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="D297" s="6" t="s">
-        <v>207</v>
+        <v>214</v>
+      </c>
+      <c r="E297" s="6" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33061,13 +33979,16 @@
         <v>2845909090</v>
       </c>
       <c r="B298" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="D298" s="6" t="s">
-        <v>209</v>
+        <v>216</v>
+      </c>
+      <c r="E298" s="6" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33075,13 +33996,16 @@
         <v>2845909090</v>
       </c>
       <c r="B299" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="D299" s="6" t="s">
-        <v>211</v>
+        <v>218</v>
+      </c>
+      <c r="E299" s="6" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33089,13 +34013,16 @@
         <v>2845909090</v>
       </c>
       <c r="B300" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="D300" s="6" t="s">
-        <v>213</v>
+        <v>220</v>
+      </c>
+      <c r="E300" s="6" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33103,13 +34030,16 @@
         <v>2845909090</v>
       </c>
       <c r="B301" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="D301" s="6" t="s">
-        <v>215</v>
+        <v>222</v>
+      </c>
+      <c r="E301" s="6" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33117,13 +34047,16 @@
         <v>2845909090</v>
       </c>
       <c r="B302" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="D302" s="6" t="s">
-        <v>217</v>
+        <v>224</v>
+      </c>
+      <c r="E302" s="6" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33131,13 +34064,16 @@
         <v>2845909090</v>
       </c>
       <c r="B303" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="D303" s="6" t="s">
-        <v>219</v>
+        <v>226</v>
+      </c>
+      <c r="E303" s="6" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33145,13 +34081,16 @@
         <v>2845909090</v>
       </c>
       <c r="B304" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="D304" s="6" t="s">
-        <v>221</v>
+        <v>228</v>
+      </c>
+      <c r="E304" s="6" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33159,13 +34098,16 @@
         <v>2845909090</v>
       </c>
       <c r="B305" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D305" s="6" t="s">
-        <v>223</v>
+        <v>230</v>
+      </c>
+      <c r="E305" s="6" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33173,13 +34115,16 @@
         <v>2845909090</v>
       </c>
       <c r="B306" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="D306" s="6" t="s">
-        <v>225</v>
+        <v>232</v>
+      </c>
+      <c r="E306" s="6" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33187,13 +34132,16 @@
         <v>2845909090</v>
       </c>
       <c r="B307" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D307" s="6" t="s">
-        <v>227</v>
+        <v>234</v>
+      </c>
+      <c r="E307" s="6" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33201,13 +34149,16 @@
         <v>2845909090</v>
       </c>
       <c r="B308" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="C308" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="D308" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="E308" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="C308" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="D308" s="6" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33215,13 +34166,16 @@
         <v>2845909090</v>
       </c>
       <c r="B309" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="D309" s="6" t="s">
-        <v>231</v>
+        <v>238</v>
+      </c>
+      <c r="E309" s="6" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33229,13 +34183,16 @@
         <v>2845909090</v>
       </c>
       <c r="B310" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D310" s="6" t="s">
-        <v>233</v>
+        <v>240</v>
+      </c>
+      <c r="E310" s="6" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33243,13 +34200,16 @@
         <v>2845909090</v>
       </c>
       <c r="B311" s="9" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C311" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="D311" s="6" t="s">
-        <v>235</v>
+        <v>242</v>
+      </c>
+      <c r="D311" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="E311" s="6" t="s">
+        <v>244</v>
       </c>
     </row>
   </sheetData>
